--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="案内状況" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="出勤情報" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="本日の出勤" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="はじめにお読みください" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="案内状況" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="出勤情報" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="本日の出勤" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,9 +30,20 @@
     </font>
     <font>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="007A5B1F"/>
-      <sz val="10"/>
+      <b val="1"/>
+      <color rgb="007A1F37"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -83,13 +95,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,129 +469,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="96" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>▼ここに入力（1行=1名）。日付・更新時刻は自動。ステータス例：空きあり／残りわずか／満員／受付終了</t>
+          <t>AROMA DAIAMOND 出勤管理テンプレート</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>エリア</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>案内時間</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>久遠 えま</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>空きあり</t>
+          <t>■ 使い方</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>四葉 まや</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>残りわずか</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>1) このファイルをGoogleドライブにアップロードし、右クリック→「Googleスプレッドシートで開く」。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>音羽 みみ</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>満員</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2) 下部の各タブ（案内状況／出勤情報／本日の出勤）に入力します。1行目の見出しは変更しないでください。</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>白雪 おと</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>受付終了</t>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>3) 各タブごとに『ファイル→共有→ウェブに公開』→対象シートを選び、形式を「カンマ区切り(.csv)」→公開→URLをコピー。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>4) GitHubの Settings→Secrets and variables→Actions→Variables に次を登録：</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     GUIDE_CSV_URL（案内状況） / SCHEDULE_CSV_URL（出勤情報） / THERAPISTS_CSV_URL（本日の出勤）</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>5) 以後、シートを更新するだけで約15分以内にサイトへ自動反映されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 入力のポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>・ステータス：空きあり／残りわずか／満員／受付終了（色分けされます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>・案内状況の日付・更新時刻は自動で入ります（入力不要）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>・出勤情報：日付ごとに複数行OK。『ラベル』は日付タブの表示名（空欄なら日付を表示）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>・本日の出勤：ハート=pink/diamond、新人=はい/空欄、SNSは;（セミコロン）区切り、写真はpublic内のファイル名（空欄可）。</t>
         </is>
       </c>
     </row>
@@ -592,7 +583,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>案内時間</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>久遠 えま</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>四葉 まや</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>残りわずか</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>音羽 みみ</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>満員</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>白雪 おと</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>受付終了</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -604,135 +725,128 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>▼日付ごとに複数行OK。ラベル=日付タブ表示名（空欄なら日付表示）。</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>日付</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>ラベル</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>エリア</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>出勤時間</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>ステータス</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>日付</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>エリア</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>出勤時間</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ステータス</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>9/16(水)</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>早乙女 せいら</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>13:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>出勤</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>2026/9/16</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>9/16(水)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>亀戸</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>早乙女 せいら</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>13:00〜翌2:00</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>出勤</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>柊 雫</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>15:00〜23:00</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2026/9/16</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>9/16(水)</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/17</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>9/17(木)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>亀戸</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>柊 雫</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>15:00〜23:00</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>空きあり</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2026/9/17</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>9/17(木)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>白雪 おと</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>13:00〜21:00</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>空きあり</t>
         </is>
@@ -743,13 +857,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -771,245 +885,238 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>▼トップの本日の出勤カード。ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名(空欄可)。</t>
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>名前</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>カップ</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>ハート</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>ラベル</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>新人</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>出勤リボン</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>サブ</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>年齢</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>カップ</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>ハート</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>新人</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>出勤リボン</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>サブ</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>SNS</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>写真</t>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>みお</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>本日 13:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>ご予約受付中</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>fgn;blue;zero2;relaxi</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>therapist-mio.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>みお</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>AJ</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>出勤</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>本日 13:00〜翌2:00</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>ご予約受付中</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>空きあり</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>fgn;blue;zero2;relaxi</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>therapist-mio.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>ゆな</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>diamond</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr"/>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>本日 15:00〜翌5:00</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>残りわずか</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>満員</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>x;zero2;relaxi;insta</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
+      <c r="P3" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -69,7 +69,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -91,11 +91,12 @@
         <color rgb="00D8C8A8"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,6 +105,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,7 +572,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>・本日の出勤：ハート=pink/diamond、新人=はい/空欄、SNSは;（セミコロン）区切り、写真はpublic内のファイル名（空欄可）。</t>
+          <t>・本日の出勤：出勤列は ○＝出勤（表示）／✖️＝欠勤（サイトから非表示）。ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
         </is>
       </c>
     </row>
@@ -863,25 +867,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="7" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -892,75 +897,80 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>出勤</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>カップ</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>ハート</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ラベル</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>新人</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>出勤リボン</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>サブ</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>写真</t>
         </is>
@@ -972,77 +982,82 @@
           <t>みお</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>AJ</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>はい</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>出勤</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>本日 13:00〜翌2:00</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>ご予約受付中</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>空きあり</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>fgn;blue;zero2;relaxi</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>therapist-mio.jpg</t>
         </is>
@@ -1054,69 +1069,145 @@
           <t>ゆな</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>diamond</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr"/>
       <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>本日 15:00〜翌5:00</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>残りわずか</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>満員</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>x;zero2;relaxi;insta</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr"/>
+      <c r="Q3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>さくら</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr"/>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>本日 12:00〜22:00</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>fgn</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="はじめにお読みください" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="案内状況" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="本日の出勤" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="出勤情報" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="本日の出勤" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -69,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -91,7 +90,6 @@
         <color rgb="00D8C8A8"/>
       </bottom>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -473,16 +471,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="96" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AROMA DAIAMOND 出勤管理テンプレート</t>
+          <t>AROMA DAIAMOND 出勤管理テンプレート（2シート運用）</t>
         </is>
       </c>
     </row>
@@ -492,87 +490,125 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ 使い方</t>
+          <t>■ シートは2つだけ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1) このファイルをGoogleドライブにアップロードし、右クリック→「Googleスプレッドシートで開く」。</t>
+          <t>① 本日の出勤 … セラピストの基本情報。ここから「本日の出勤カード」と「只今の案内状況」を自動表示。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2) 下部の各タブ（案内状況／出勤情報／本日の出勤）に入力します。1行目の見出しは変更しないでください。</t>
+          <t>② 出勤情報 … 日付ごとの出勤（日付タブ）。写真等は①の名前と一致させれば自動表示。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3) 各タブごとに『ファイル→共有→ウェブに公開』→対象シートを選び、形式を「カンマ区切り(.csv)」→公開→URLをコピー。</t>
+          <t>※「案内状況」は①から自動生成されるので、手入力シートは不要です。</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>4) GitHubの Settings→Secrets and variables→Actions→Variables に次を登録：</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     GUIDE_CSV_URL（案内状況） / SCHEDULE_CSV_URL（出勤情報） / THERAPISTS_CSV_URL（本日の出勤）</t>
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>■ 使い方</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>5) 以後、シートを更新するだけで約15分以内にサイトへ自動反映されます。</t>
+          <t>1) Googleドライブにアップ→Googleスプレッドシートで開く（1行目の見出しは変更しない）。</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2) ①本日の出勤 と ②出勤情報 の各タブを『ファイル→共有→ウェブに公開(CSV)』で公開しURLをコピー。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>■ 入力のポイント</t>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>3) GitHubのSettings→Secrets and variables→Actions→Variablesに登録：</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>・ステータス：空きあり／残りわずか／満員／受付終了（色分けされます）</t>
+          <t xml:space="preserve">     THERAPISTS_CSV_URL＝①本日の出勤 ／ SCHEDULE_CSV_URL＝②出勤情報</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>・案内状況の日付・更新時刻は自動で入ります（入力不要）。</t>
+          <t xml:space="preserve">     （以前のGUIDE_CSV_URLは不要です。残っていても無視されます）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>・出勤情報：日付ごとに複数行OK。『ラベル』は日付タブの表示名（空欄なら日付を表示）。</t>
+          <t>4) 約15分以内に自動反映。すぐ反映は Actions→Deploy to GitHub Pages→Run workflow。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>・本日の出勤：出勤列は ○＝出勤（表示）／✖️＝欠勤（サイトから非表示）。ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■ 入力のポイント</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>・出勤：○＝出勤（表示）／✖️＝欠勤（3か所すべてから非表示）。空欄は表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>・案内時刻：只今の案内状況に出す時刻（例 15:30〜）。空欄なら時刻なしで表示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>・ステータス：空きあり／残りわずか／満員／受付終了（色分け）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>・出勤情報の名前は、本日の出勤の名前と完全一致させる（写真・スペックが自動表示）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>・ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
         </is>
       </c>
     </row>
@@ -587,124 +623,360 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="22" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>エリア</t>
+          <t>名前</t>
         </is>
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>出勤</t>
         </is>
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
-          <t>案内時間</t>
+          <t>案内時刻</t>
         </is>
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>年齢</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>カップ</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>ハート</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>ラベル</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>新人</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>出勤リボン</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>スケジュール</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>サブ</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
           <t>ステータス</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>SNS</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>写真</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>久遠 えま</t>
+          <t>みお</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:30〜</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>本日 13:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>ご予約受付中</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
           <t>空きあり</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>fgn;blue;zero2;relaxi</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>therapist-mio.jpg</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>四葉 まや</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
+          <t>ゆな</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr"/>
       <c r="D3" s="5" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr"/>
+      <c r="M3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>本日 15:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
           <t>残りわずか</t>
         </is>
       </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>満員</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>x;zero2;relaxi;insta</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>音羽 みみ</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
+          <t>さくら</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>満員</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>亀戸</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>白雪 おと</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>受付終了</t>
-        </is>
-      </c>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr"/>
+      <c r="M4" s="5" t="inlineStr"/>
+      <c r="N4" s="5" t="inlineStr">
+        <is>
+          <t>本日 12:00〜22:00</t>
+        </is>
+      </c>
+      <c r="O4" s="5" t="inlineStr"/>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>fgn</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -717,15 +989,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -759,6 +1032,11 @@
           <t>ステータス</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -778,7 +1056,7 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>早乙女 せいら</t>
+          <t>みお</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -788,7 +1066,12 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>出勤</t>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -810,7 +1093,7 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>柊 雫</t>
+          <t>ゆな</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -820,7 +1103,12 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>空きあり</t>
+          <t>満員</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
         </is>
       </c>
     </row>
@@ -842,12 +1130,12 @@
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>白雪 おと</t>
+          <t>みお</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>13:00〜21:00</t>
+          <t>18:00〜翌2:00</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
@@ -855,359 +1143,11 @@
           <t>空きあり</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="7" customWidth="1" min="6" max="6"/>
-    <col width="6" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>名前</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>出勤</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>年齢</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>カップ</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>ハート</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>ラベル</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>新人</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>出勤リボン</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>スケジュール</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>サブ</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>ステータス</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>SNS</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>写真</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>みお</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
-        <is>
-          <t>AJ</t>
-        </is>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>はい</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>出勤</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>本日 13:00〜翌2:00</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="inlineStr">
-        <is>
-          <t>ご予約受付中</t>
-        </is>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>空きあり</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>fgn;blue;zero2;relaxi</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="inlineStr">
-        <is>
-          <t>therapist-mio.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>ゆな</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>○</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>diamond</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="inlineStr">
-        <is>
-          <t>◆</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="inlineStr"/>
-      <c r="L3" s="5" t="inlineStr"/>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>本日 15:00〜翌5:00</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="inlineStr">
-        <is>
-          <t>残りわずか</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>満員</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>x;zero2;relaxi;insta</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>さくら</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>pink</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="inlineStr">
-        <is>
-          <t>AJ</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="inlineStr"/>
-      <c r="L4" s="5" t="inlineStr"/>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>本日 12:00〜22:00</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>空きあり</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>fgn</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -68,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -90,6 +90,7 @@
         <color rgb="00D8C8A8"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -608,7 +609,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>・ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
+          <t>・タグ：セラピスト一覧ページに出す特徴（例 ピュア妹系;スレンダー美女…）。;（セミコロン）区切り。ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
         </is>
       </c>
     </row>
@@ -623,7 +624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -642,8 +643,9 @@
     <col width="20" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -729,10 +731,15 @@
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
+          <t>タグ</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>写真</t>
         </is>
@@ -821,10 +828,15 @@
       </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
+          <t>ピュア妹系;スレンダー美女;透明感抜群;愛情たっぷり</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
           <t>fgn;blue;zero2;relaxi</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>therapist-mio.jpg</t>
         </is>
@@ -901,10 +913,15 @@
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
+          <t>超絶美女;高身長;高リピート率;大人の魅力</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
           <t>x;zero2;relaxi;insta</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr"/>
+      <c r="S3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -973,10 +990,15 @@
       </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
+          <t>清楚系;美脚;小顔美人;癒やし上手</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
           <t>fgn</t>
         </is>
       </c>
-      <c r="R4" s="5" t="inlineStr"/>
+      <c r="S4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -610,6 +610,27 @@
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>・タグ：セラピスト一覧ページに出す特徴（例 ピュア妹系;スレンダー美女…）。;（セミコロン）区切り。ハート=pink/diamond、新人=はい/空欄、SNSは;区切り、写真はpublic内のファイル名（空欄可）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>・在籍（本日の出勤）：在籍＝表示／退店・休業＝全ページから除外。日々の勤怠は「出勤(○/✖️)」で。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>・区分（出勤情報）：確定＝サイト表示／申請中・希望休＝社内のみ（非表示）。シフト管理に。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>・上記以外の列（連絡先・本名・給与・メモ・開始/終了 等）は自由に追加OK。サイトには出ません。</t>
         </is>
       </c>
     </row>
@@ -624,28 +645,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
     <col width="6" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="7" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,90 +678,95 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>出勤</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>案内時刻</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>年齢</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>カップ</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>W</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>ハート</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>ラベル</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>新人</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>出勤リボン</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>スケジュール</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>サブ</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>タグ</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>SNS</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>写真</t>
         </is>
@@ -753,90 +780,95 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>15:30〜</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>158</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>86</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>AJ</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>はい</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>出勤</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>本日 13:00〜翌2:00</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>ご予約受付中</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>空きあり</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>ピュア妹系;スレンダー美女;透明感抜群;愛情たっぷり</t>
         </is>
       </c>
-      <c r="R2" s="5" t="inlineStr">
+      <c r="S2" s="5" t="inlineStr">
         <is>
           <t>fgn;blue;zero2;relaxi</t>
         </is>
       </c>
-      <c r="S2" s="5" t="inlineStr">
+      <c r="T2" s="5" t="inlineStr">
         <is>
           <t>therapist-mio.jpg</t>
         </is>
@@ -850,78 +882,83 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
           <t>○</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr"/>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr"/>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>diamond</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>◆</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr"/>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr"/>
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>本日 15:00〜翌5:00</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>残りわずか</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>満員</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>超絶美女;高身長;高リピート率;大人の魅力</t>
         </is>
       </c>
-      <c r="R3" s="5" t="inlineStr">
+      <c r="S3" s="5" t="inlineStr">
         <is>
           <t>x;zero2;relaxi;insta</t>
         </is>
       </c>
-      <c r="S3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -931,74 +968,63 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>✖️</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
+          <t>退店</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>160</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>pink</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>AJ</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr"/>
       <c r="M4" s="5" t="inlineStr"/>
-      <c r="N4" s="5" t="inlineStr">
-        <is>
-          <t>本日 12:00〜22:00</t>
-        </is>
-      </c>
+      <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>空きあり</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="inlineStr">
-        <is>
-          <t>清楚系;美脚;小顔美人;癒やし上手</t>
-        </is>
-      </c>
+      <c r="P4" s="5" t="inlineStr"/>
+      <c r="Q4" s="5" t="inlineStr"/>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>fgn</t>
+          <t>清楚系;美脚</t>
         </is>
       </c>
       <c r="S4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1011,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1021,6 +1047,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,6 +1086,11 @@
           <t>出勤</t>
         </is>
       </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1096,6 +1128,11 @@
           <t>○</t>
         </is>
       </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1133,6 +1170,11 @@
           <t>○</t>
         </is>
       </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1168,6 +1210,11 @@
       <c r="G4" s="6" t="inlineStr">
         <is>
           <t>○</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>申請中</t>
         </is>
       </c>
     </row>

--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -10,6 +10,7 @@
     <sheet name="はじめにお読みください" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="本日の出勤" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="出勤情報" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="週間シフト表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,8 +55,30 @@
       <name val="Arial"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009A8654"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="009A8654"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="007A1F37"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00555555"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -65,6 +88,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00911F3F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF3E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F3ECDD"/>
       </patternFill>
     </fill>
   </fills>
@@ -95,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +140,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1037,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1089,7 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1091,6 +1133,11 @@
           <t>区分</t>
         </is>
       </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>キー(自動)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -1133,6 +1180,10 @@
           <t>確定</t>
         </is>
       </c>
+      <c r="I2" s="8">
+        <f>IF($D2="","",$D2&amp;"|"&amp;$B2)</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -1175,6 +1226,10 @@
           <t>確定</t>
         </is>
       </c>
+      <c r="I3" s="8">
+        <f>IF($D3="","",$D3&amp;"|"&amp;$B3)</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1216,9 +1271,2306 @@
         <is>
           <t>申請中</t>
         </is>
+      </c>
+      <c r="I4" s="8">
+        <f>IF($D4="","",$D4&amp;"|"&amp;$B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="I5" s="8">
+        <f>IF($D5="","",$D5&amp;"|"&amp;$B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="I6" s="8">
+        <f>IF($D6="","",$D6&amp;"|"&amp;$B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="I7" s="8">
+        <f>IF($D7="","",$D7&amp;"|"&amp;$B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="I8" s="8">
+        <f>IF($D8="","",$D8&amp;"|"&amp;$B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="I9" s="8">
+        <f>IF($D9="","",$D9&amp;"|"&amp;$B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="I10" s="8">
+        <f>IF($D10="","",$D10&amp;"|"&amp;$B10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="I11" s="8">
+        <f>IF($D11="","",$D11&amp;"|"&amp;$B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="I12" s="8">
+        <f>IF($D12="","",$D12&amp;"|"&amp;$B12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="I13" s="8">
+        <f>IF($D13="","",$D13&amp;"|"&amp;$B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="I14" s="8">
+        <f>IF($D14="","",$D14&amp;"|"&amp;$B14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="I15" s="8">
+        <f>IF($D15="","",$D15&amp;"|"&amp;$B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="I16" s="8">
+        <f>IF($D16="","",$D16&amp;"|"&amp;$B16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="I17" s="8">
+        <f>IF($D17="","",$D17&amp;"|"&amp;$B17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="I18" s="8">
+        <f>IF($D18="","",$D18&amp;"|"&amp;$B18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="I19" s="8">
+        <f>IF($D19="","",$D19&amp;"|"&amp;$B19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="I20" s="8">
+        <f>IF($D20="","",$D20&amp;"|"&amp;$B20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="I21" s="8">
+        <f>IF($D21="","",$D21&amp;"|"&amp;$B21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="I22" s="8">
+        <f>IF($D22="","",$D22&amp;"|"&amp;$B22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="I23" s="8">
+        <f>IF($D23="","",$D23&amp;"|"&amp;$B23)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="I24" s="8">
+        <f>IF($D24="","",$D24&amp;"|"&amp;$B24)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="I25" s="8">
+        <f>IF($D25="","",$D25&amp;"|"&amp;$B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="I26" s="8">
+        <f>IF($D26="","",$D26&amp;"|"&amp;$B26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="I27" s="8">
+        <f>IF($D27="","",$D27&amp;"|"&amp;$B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="I28" s="8">
+        <f>IF($D28="","",$D28&amp;"|"&amp;$B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="I29" s="8">
+        <f>IF($D29="","",$D29&amp;"|"&amp;$B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="I30" s="8">
+        <f>IF($D30="","",$D30&amp;"|"&amp;$B30)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="I31" s="8">
+        <f>IF($D31="","",$D31&amp;"|"&amp;$B31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="I32" s="8">
+        <f>IF($D32="","",$D32&amp;"|"&amp;$B32)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="I33" s="8">
+        <f>IF($D33="","",$D33&amp;"|"&amp;$B33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="I34" s="8">
+        <f>IF($D34="","",$D34&amp;"|"&amp;$B34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="I35" s="8">
+        <f>IF($D35="","",$D35&amp;"|"&amp;$B35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="I36" s="8">
+        <f>IF($D36="","",$D36&amp;"|"&amp;$B36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="I37" s="8">
+        <f>IF($D37="","",$D37&amp;"|"&amp;$B37)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="I38" s="8">
+        <f>IF($D38="","",$D38&amp;"|"&amp;$B38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="I39" s="8">
+        <f>IF($D39="","",$D39&amp;"|"&amp;$B39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="I40" s="8">
+        <f>IF($D40="","",$D40&amp;"|"&amp;$B40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="I41" s="8">
+        <f>IF($D41="","",$D41&amp;"|"&amp;$B41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="I42" s="8">
+        <f>IF($D42="","",$D42&amp;"|"&amp;$B42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="I43" s="8">
+        <f>IF($D43="","",$D43&amp;"|"&amp;$B43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="I44" s="8">
+        <f>IF($D44="","",$D44&amp;"|"&amp;$B44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="I45" s="8">
+        <f>IF($D45="","",$D45&amp;"|"&amp;$B45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="I46" s="8">
+        <f>IF($D46="","",$D46&amp;"|"&amp;$B46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="I47" s="8">
+        <f>IF($D47="","",$D47&amp;"|"&amp;$B47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="I48" s="8">
+        <f>IF($D48="","",$D48&amp;"|"&amp;$B48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="I49" s="8">
+        <f>IF($D49="","",$D49&amp;"|"&amp;$B49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="I50" s="8">
+        <f>IF($D50="","",$D50&amp;"|"&amp;$B50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="I51" s="8">
+        <f>IF($D51="","",$D51&amp;"|"&amp;$B51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="I52" s="8">
+        <f>IF($D52="","",$D52&amp;"|"&amp;$B52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="I53" s="8">
+        <f>IF($D53="","",$D53&amp;"|"&amp;$B53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="I54" s="8">
+        <f>IF($D54="","",$D54&amp;"|"&amp;$B54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="I55" s="8">
+        <f>IF($D55="","",$D55&amp;"|"&amp;$B55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="I56" s="8">
+        <f>IF($D56="","",$D56&amp;"|"&amp;$B56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="I57" s="8">
+        <f>IF($D57="","",$D57&amp;"|"&amp;$B57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="I58" s="8">
+        <f>IF($D58="","",$D58&amp;"|"&amp;$B58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="I59" s="8">
+        <f>IF($D59="","",$D59&amp;"|"&amp;$B59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="I60" s="8">
+        <f>IF($D60="","",$D60&amp;"|"&amp;$B60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="I61" s="8">
+        <f>IF($D61="","",$D61&amp;"|"&amp;$B61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="I62" s="8">
+        <f>IF($D62="","",$D62&amp;"|"&amp;$B62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="I63" s="8">
+        <f>IF($D63="","",$D63&amp;"|"&amp;$B63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="I64" s="8">
+        <f>IF($D64="","",$D64&amp;"|"&amp;$B64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="I65" s="8">
+        <f>IF($D65="","",$D65&amp;"|"&amp;$B65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="I66" s="8">
+        <f>IF($D66="","",$D66&amp;"|"&amp;$B66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="I67" s="8">
+        <f>IF($D67="","",$D67&amp;"|"&amp;$B67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="I68" s="8">
+        <f>IF($D68="","",$D68&amp;"|"&amp;$B68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="I69" s="8">
+        <f>IF($D69="","",$D69&amp;"|"&amp;$B69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="I70" s="8">
+        <f>IF($D70="","",$D70&amp;"|"&amp;$B70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="I71" s="8">
+        <f>IF($D71="","",$D71&amp;"|"&amp;$B71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="I72" s="8">
+        <f>IF($D72="","",$D72&amp;"|"&amp;$B72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="I73" s="8">
+        <f>IF($D73="","",$D73&amp;"|"&amp;$B73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="I74" s="8">
+        <f>IF($D74="","",$D74&amp;"|"&amp;$B74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="I75" s="8">
+        <f>IF($D75="","",$D75&amp;"|"&amp;$B75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="I76" s="8">
+        <f>IF($D76="","",$D76&amp;"|"&amp;$B76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="I77" s="8">
+        <f>IF($D77="","",$D77&amp;"|"&amp;$B77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="I78" s="8">
+        <f>IF($D78="","",$D78&amp;"|"&amp;$B78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="I79" s="8">
+        <f>IF($D79="","",$D79&amp;"|"&amp;$B79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="I80" s="8">
+        <f>IF($D80="","",$D80&amp;"|"&amp;$B80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="I81" s="8">
+        <f>IF($D81="","",$D81&amp;"|"&amp;$B81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="I82" s="8">
+        <f>IF($D82="","",$D82&amp;"|"&amp;$B82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="I83" s="8">
+        <f>IF($D83="","",$D83&amp;"|"&amp;$B83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="I84" s="8">
+        <f>IF($D84="","",$D84&amp;"|"&amp;$B84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="I85" s="8">
+        <f>IF($D85="","",$D85&amp;"|"&amp;$B85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="I86" s="8">
+        <f>IF($D86="","",$D86&amp;"|"&amp;$B86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="I87" s="8">
+        <f>IF($D87="","",$D87&amp;"|"&amp;$B87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="I88" s="8">
+        <f>IF($D88="","",$D88&amp;"|"&amp;$B88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="I89" s="8">
+        <f>IF($D89="","",$D89&amp;"|"&amp;$B89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="I90" s="8">
+        <f>IF($D90="","",$D90&amp;"|"&amp;$B90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="I91" s="8">
+        <f>IF($D91="","",$D91&amp;"|"&amp;$B91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="I92" s="8">
+        <f>IF($D92="","",$D92&amp;"|"&amp;$B92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="I93" s="8">
+        <f>IF($D93="","",$D93&amp;"|"&amp;$B93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="I94" s="8">
+        <f>IF($D94="","",$D94&amp;"|"&amp;$B94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="I95" s="8">
+        <f>IF($D95="","",$D95&amp;"|"&amp;$B95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="I96" s="8">
+        <f>IF($D96="","",$D96&amp;"|"&amp;$B96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="I97" s="8">
+        <f>IF($D97="","",$D97&amp;"|"&amp;$B97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="I98" s="8">
+        <f>IF($D98="","",$D98&amp;"|"&amp;$B98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="I99" s="8">
+        <f>IF($D99="","",$D99&amp;"|"&amp;$B99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="I100" s="8">
+        <f>IF($D100="","",$D100&amp;"|"&amp;$B100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="I101" s="8">
+        <f>IF($D101="","",$D101&amp;"|"&amp;$B101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="I102" s="8">
+        <f>IF($D102="","",$D102&amp;"|"&amp;$B102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="I103" s="8">
+        <f>IF($D103="","",$D103&amp;"|"&amp;$B103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="I104" s="8">
+        <f>IF($D104="","",$D104&amp;"|"&amp;$B104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="I105" s="8">
+        <f>IF($D105="","",$D105&amp;"|"&amp;$B105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="I106" s="8">
+        <f>IF($D106="","",$D106&amp;"|"&amp;$B106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="I107" s="8">
+        <f>IF($D107="","",$D107&amp;"|"&amp;$B107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="I108" s="8">
+        <f>IF($D108="","",$D108&amp;"|"&amp;$B108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="I109" s="8">
+        <f>IF($D109="","",$D109&amp;"|"&amp;$B109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="I110" s="8">
+        <f>IF($D110="","",$D110&amp;"|"&amp;$B110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="I111" s="8">
+        <f>IF($D111="","",$D111&amp;"|"&amp;$B111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="I112" s="8">
+        <f>IF($D112="","",$D112&amp;"|"&amp;$B112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="I113" s="8">
+        <f>IF($D113="","",$D113&amp;"|"&amp;$B113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="I114" s="8">
+        <f>IF($D114="","",$D114&amp;"|"&amp;$B114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="I115" s="8">
+        <f>IF($D115="","",$D115&amp;"|"&amp;$B115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="I116" s="8">
+        <f>IF($D116="","",$D116&amp;"|"&amp;$B116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="I117" s="8">
+        <f>IF($D117="","",$D117&amp;"|"&amp;$B117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="I118" s="8">
+        <f>IF($D118="","",$D118&amp;"|"&amp;$B118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="I119" s="8">
+        <f>IF($D119="","",$D119&amp;"|"&amp;$B119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="I120" s="8">
+        <f>IF($D120="","",$D120&amp;"|"&amp;$B120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="I121" s="8">
+        <f>IF($D121="","",$D121&amp;"|"&amp;$B121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="I122" s="8">
+        <f>IF($D122="","",$D122&amp;"|"&amp;$B122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="I123" s="8">
+        <f>IF($D123="","",$D123&amp;"|"&amp;$B123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="I124" s="8">
+        <f>IF($D124="","",$D124&amp;"|"&amp;$B124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="I125" s="8">
+        <f>IF($D125="","",$D125&amp;"|"&amp;$B125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="I126" s="8">
+        <f>IF($D126="","",$D126&amp;"|"&amp;$B126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="I127" s="8">
+        <f>IF($D127="","",$D127&amp;"|"&amp;$B127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="I128" s="8">
+        <f>IF($D128="","",$D128&amp;"|"&amp;$B128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="I129" s="8">
+        <f>IF($D129="","",$D129&amp;"|"&amp;$B129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="I130" s="8">
+        <f>IF($D130="","",$D130&amp;"|"&amp;$B130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="I131" s="8">
+        <f>IF($D131="","",$D131&amp;"|"&amp;$B131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="I132" s="8">
+        <f>IF($D132="","",$D132&amp;"|"&amp;$B132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="I133" s="8">
+        <f>IF($D133="","",$D133&amp;"|"&amp;$B133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="I134" s="8">
+        <f>IF($D134="","",$D134&amp;"|"&amp;$B134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="I135" s="8">
+        <f>IF($D135="","",$D135&amp;"|"&amp;$B135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="I136" s="8">
+        <f>IF($D136="","",$D136&amp;"|"&amp;$B136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="I137" s="8">
+        <f>IF($D137="","",$D137&amp;"|"&amp;$B137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="I138" s="8">
+        <f>IF($D138="","",$D138&amp;"|"&amp;$B138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="I139" s="8">
+        <f>IF($D139="","",$D139&amp;"|"&amp;$B139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="I140" s="8">
+        <f>IF($D140="","",$D140&amp;"|"&amp;$B140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="I141" s="8">
+        <f>IF($D141="","",$D141&amp;"|"&amp;$B141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="I142" s="8">
+        <f>IF($D142="","",$D142&amp;"|"&amp;$B142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="I143" s="8">
+        <f>IF($D143="","",$D143&amp;"|"&amp;$B143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="I144" s="8">
+        <f>IF($D144="","",$D144&amp;"|"&amp;$B144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="I145" s="8">
+        <f>IF($D145="","",$D145&amp;"|"&amp;$B145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="I146" s="8">
+        <f>IF($D146="","",$D146&amp;"|"&amp;$B146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="I147" s="8">
+        <f>IF($D147="","",$D147&amp;"|"&amp;$B147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="I148" s="8">
+        <f>IF($D148="","",$D148&amp;"|"&amp;$B148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="I149" s="8">
+        <f>IF($D149="","",$D149&amp;"|"&amp;$B149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="I150" s="8">
+        <f>IF($D150="","",$D150&amp;"|"&amp;$B150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="I151" s="8">
+        <f>IF($D151="","",$D151&amp;"|"&amp;$B151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="I152" s="8">
+        <f>IF($D152="","",$D152&amp;"|"&amp;$B152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="I153" s="8">
+        <f>IF($D153="","",$D153&amp;"|"&amp;$B153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="I154" s="8">
+        <f>IF($D154="","",$D154&amp;"|"&amp;$B154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="I155" s="8">
+        <f>IF($D155="","",$D155&amp;"|"&amp;$B155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="I156" s="8">
+        <f>IF($D156="","",$D156&amp;"|"&amp;$B156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="I157" s="8">
+        <f>IF($D157="","",$D157&amp;"|"&amp;$B157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="I158" s="8">
+        <f>IF($D158="","",$D158&amp;"|"&amp;$B158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="I159" s="8">
+        <f>IF($D159="","",$D159&amp;"|"&amp;$B159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="I160" s="8">
+        <f>IF($D160="","",$D160&amp;"|"&amp;$B160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="I161" s="8">
+        <f>IF($D161="","",$D161&amp;"|"&amp;$B161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="I162" s="8">
+        <f>IF($D162="","",$D162&amp;"|"&amp;$B162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="I163" s="8">
+        <f>IF($D163="","",$D163&amp;"|"&amp;$B163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="I164" s="8">
+        <f>IF($D164="","",$D164&amp;"|"&amp;$B164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="I165" s="8">
+        <f>IF($D165="","",$D165&amp;"|"&amp;$B165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="I166" s="8">
+        <f>IF($D166="","",$D166&amp;"|"&amp;$B166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="I167" s="8">
+        <f>IF($D167="","",$D167&amp;"|"&amp;$B167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="I168" s="8">
+        <f>IF($D168="","",$D168&amp;"|"&amp;$B168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="I169" s="8">
+        <f>IF($D169="","",$D169&amp;"|"&amp;$B169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="I170" s="8">
+        <f>IF($D170="","",$D170&amp;"|"&amp;$B170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="I171" s="8">
+        <f>IF($D171="","",$D171&amp;"|"&amp;$B171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="I172" s="8">
+        <f>IF($D172="","",$D172&amp;"|"&amp;$B172)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="I173" s="8">
+        <f>IF($D173="","",$D173&amp;"|"&amp;$B173)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="I174" s="8">
+        <f>IF($D174="","",$D174&amp;"|"&amp;$B174)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="I175" s="8">
+        <f>IF($D175="","",$D175&amp;"|"&amp;$B175)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="I176" s="8">
+        <f>IF($D176="","",$D176&amp;"|"&amp;$B176)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="I177" s="8">
+        <f>IF($D177="","",$D177&amp;"|"&amp;$B177)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="I178" s="8">
+        <f>IF($D178="","",$D178&amp;"|"&amp;$B178)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="I179" s="8">
+        <f>IF($D179="","",$D179&amp;"|"&amp;$B179)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="I180" s="8">
+        <f>IF($D180="","",$D180&amp;"|"&amp;$B180)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="I181" s="8">
+        <f>IF($D181="","",$D181&amp;"|"&amp;$B181)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="I182" s="8">
+        <f>IF($D182="","",$D182&amp;"|"&amp;$B182)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="I183" s="8">
+        <f>IF($D183="","",$D183&amp;"|"&amp;$B183)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="I184" s="8">
+        <f>IF($D184="","",$D184&amp;"|"&amp;$B184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="I185" s="8">
+        <f>IF($D185="","",$D185&amp;"|"&amp;$B185)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="I186" s="8">
+        <f>IF($D186="","",$D186&amp;"|"&amp;$B186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="I187" s="8">
+        <f>IF($D187="","",$D187&amp;"|"&amp;$B187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="I188" s="8">
+        <f>IF($D188="","",$D188&amp;"|"&amp;$B188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="I189" s="8">
+        <f>IF($D189="","",$D189&amp;"|"&amp;$B189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="I190" s="8">
+        <f>IF($D190="","",$D190&amp;"|"&amp;$B190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="I191" s="8">
+        <f>IF($D191="","",$D191&amp;"|"&amp;$B191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="I192" s="8">
+        <f>IF($D192="","",$D192&amp;"|"&amp;$B192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="I193" s="8">
+        <f>IF($D193="","",$D193&amp;"|"&amp;$B193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="I194" s="8">
+        <f>IF($D194="","",$D194&amp;"|"&amp;$B194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="I195" s="8">
+        <f>IF($D195="","",$D195&amp;"|"&amp;$B195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="I196" s="8">
+        <f>IF($D196="","",$D196&amp;"|"&amp;$B196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="I197" s="8">
+        <f>IF($D197="","",$D197&amp;"|"&amp;$B197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="I198" s="8">
+        <f>IF($D198="","",$D198&amp;"|"&amp;$B198)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="I199" s="8">
+        <f>IF($D199="","",$D199&amp;"|"&amp;$B199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="I200" s="8">
+        <f>IF($D200="","",$D200&amp;"|"&amp;$B200)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>■ 週間シフト表（「出勤情報」を編集すると自動で更新されます）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>セラピスト＼日付</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>9/16(水)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>9/17(木)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>9/18(金)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>9/19(土)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>9/20(日)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>9/21(月)</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>9/22(火)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10">
+        <f>IF('本日の出勤'!A2="","",'本日の出勤'!A2)</f>
+        <v/>
+      </c>
+      <c r="B4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H4" s="11">
+        <f>IF($A4="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A4&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10">
+        <f>IF('本日の出勤'!A3="","",'本日の出勤'!A3)</f>
+        <v/>
+      </c>
+      <c r="B5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H5" s="11">
+        <f>IF($A5="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A5&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10">
+        <f>IF('本日の出勤'!A4="","",'本日の出勤'!A4)</f>
+        <v/>
+      </c>
+      <c r="B6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H6" s="11">
+        <f>IF($A6="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A6&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10">
+        <f>IF('本日の出勤'!A5="","",'本日の出勤'!A5)</f>
+        <v/>
+      </c>
+      <c r="B7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H7" s="11">
+        <f>IF($A7="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A7&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10">
+        <f>IF('本日の出勤'!A6="","",'本日の出勤'!A6)</f>
+        <v/>
+      </c>
+      <c r="B8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H8" s="11">
+        <f>IF($A8="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A8&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10">
+        <f>IF('本日の出勤'!A7="","",'本日の出勤'!A7)</f>
+        <v/>
+      </c>
+      <c r="B9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H9" s="11">
+        <f>IF($A9="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A9&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10">
+        <f>IF('本日の出勤'!A8="","",'本日の出勤'!A8)</f>
+        <v/>
+      </c>
+      <c r="B10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H10" s="11">
+        <f>IF($A10="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A10&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10">
+        <f>IF('本日の出勤'!A9="","",'本日の出勤'!A9)</f>
+        <v/>
+      </c>
+      <c r="B11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H11" s="11">
+        <f>IF($A11="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A11&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10">
+        <f>IF('本日の出勤'!A10="","",'本日の出勤'!A10)</f>
+        <v/>
+      </c>
+      <c r="B12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H12" s="11">
+        <f>IF($A12="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A12&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10">
+        <f>IF('本日の出勤'!A11="","",'本日の出勤'!A11)</f>
+        <v/>
+      </c>
+      <c r="B13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H13" s="11">
+        <f>IF($A13="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A13&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10">
+        <f>IF('本日の出勤'!A12="","",'本日の出勤'!A12)</f>
+        <v/>
+      </c>
+      <c r="B14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H14" s="11">
+        <f>IF($A14="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A14&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10">
+        <f>IF('本日の出勤'!A13="","",'本日の出勤'!A13)</f>
+        <v/>
+      </c>
+      <c r="B15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H15" s="11">
+        <f>IF($A15="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A15&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10">
+        <f>IF('本日の出勤'!A14="","",'本日の出勤'!A14)</f>
+        <v/>
+      </c>
+      <c r="B16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H16" s="11">
+        <f>IF($A16="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A16&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10">
+        <f>IF('本日の出勤'!A15="","",'本日の出勤'!A15)</f>
+        <v/>
+      </c>
+      <c r="B17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>IF($A17="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A17&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10">
+        <f>IF('本日の出勤'!A16="","",'本日の出勤'!A16)</f>
+        <v/>
+      </c>
+      <c r="B18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H18" s="11">
+        <f>IF($A18="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A18&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10">
+        <f>IF('本日の出勤'!A17="","",'本日の出勤'!A17)</f>
+        <v/>
+      </c>
+      <c r="B19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H19" s="11">
+        <f>IF($A19="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A19&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10">
+        <f>IF('本日の出勤'!A18="","",'本日の出勤'!A18)</f>
+        <v/>
+      </c>
+      <c r="B20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H20" s="11">
+        <f>IF($A20="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A20&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10">
+        <f>IF('本日の出勤'!A19="","",'本日の出勤'!A19)</f>
+        <v/>
+      </c>
+      <c r="B21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H21" s="11">
+        <f>IF($A21="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A21&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10">
+        <f>IF('本日の出勤'!A20="","",'本日の出勤'!A20)</f>
+        <v/>
+      </c>
+      <c r="B22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H22" s="11">
+        <f>IF($A22="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A22&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10">
+        <f>IF('本日の出勤'!A21="","",'本日の出勤'!A21)</f>
+        <v/>
+      </c>
+      <c r="B23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H23" s="11">
+        <f>IF($A23="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A23&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10">
+        <f>IF('本日の出勤'!A22="","",'本日の出勤'!A22)</f>
+        <v/>
+      </c>
+      <c r="B24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H24" s="11">
+        <f>IF($A24="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A24&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10">
+        <f>IF('本日の出勤'!A23="","",'本日の出勤'!A23)</f>
+        <v/>
+      </c>
+      <c r="B25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H25" s="11">
+        <f>IF($A25="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A25&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10">
+        <f>IF('本日の出勤'!A24="","",'本日の出勤'!A24)</f>
+        <v/>
+      </c>
+      <c r="B26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H26" s="11">
+        <f>IF($A26="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A26&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10">
+        <f>IF('本日の出勤'!A25="","",'本日の出勤'!A25)</f>
+        <v/>
+      </c>
+      <c r="B27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H27" s="11">
+        <f>IF($A27="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A27&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10">
+        <f>IF('本日の出勤'!A26="","",'本日の出勤'!A26)</f>
+        <v/>
+      </c>
+      <c r="B28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H28" s="11">
+        <f>IF($A28="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A28&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10">
+        <f>IF('本日の出勤'!A27="","",'本日の出勤'!A27)</f>
+        <v/>
+      </c>
+      <c r="B29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H29" s="11">
+        <f>IF($A29="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A29&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10">
+        <f>IF('本日の出勤'!A28="","",'本日の出勤'!A28)</f>
+        <v/>
+      </c>
+      <c r="B30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H30" s="11">
+        <f>IF($A30="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A30&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10">
+        <f>IF('本日の出勤'!A29="","",'本日の出勤'!A29)</f>
+        <v/>
+      </c>
+      <c r="B31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H31" s="11">
+        <f>IF($A31="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A31&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10">
+        <f>IF('本日の出勤'!A30="","",'本日の出勤'!A30)</f>
+        <v/>
+      </c>
+      <c r="B32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H32" s="11">
+        <f>IF($A32="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A32&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10">
+        <f>IF('本日の出勤'!A31="","",'本日の出勤'!A31)</f>
+        <v/>
+      </c>
+      <c r="B33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;B$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="C33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;C$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="D33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;D$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="E33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;E$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="F33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;F$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="G33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;G$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+      <c r="H33" s="11">
+        <f>IF($A33="","",IFERROR(INDEX(出勤情報!$E$2:$E$200,MATCH($A33&amp;"|"&amp;H$3,出勤情報!$I$2:$I$200,0)),""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>使い方：3行目の日付ラベルを今週の日付に変更してください（「出勤情報」のラベル列と同じ表記）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>各セルには「出勤情報」の出勤時間が自動表示されます（空欄＝その日は休み/未登録）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>名前は「本日の出勤」シートから自動取得します。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
+++ b/docs/AROMA_DAIAMOND_出勤管理_テンプレート.xlsx
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -148,6 +148,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -686,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -918,7 +921,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>ゆな</t>
+          <t>花恋</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
@@ -931,35 +934,39 @@
           <t>○</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>16:00〜</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>160</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H3" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K3" s="5" t="inlineStr">
@@ -973,75 +980,87 @@
         </is>
       </c>
       <c r="M3" s="5" t="inlineStr"/>
-      <c r="N3" s="5" t="inlineStr"/>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>本日 15:00〜翌5:00</t>
+          <t>本日 16:00〜翌3:00</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>残りわずか</t>
+          <t>受付中</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>満員</t>
+          <t>空きあり</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>超絶美女;高身長;高リピート率;大人の魅力</t>
+          <t>清楚系;笑顔が素敵;美乳;神対応</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>x;zero2;relaxi;insta</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr"/>
+          <t>fgn;zero2;relaxi;insta</t>
+        </is>
+      </c>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>therapist-karen.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ゆな</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>退店</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
       <c r="D4" s="5" t="inlineStr"/>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>162</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>84</t>
         </is>
       </c>
       <c r="K4" s="5" t="inlineStr">
@@ -1056,16 +1075,634 @@
       </c>
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
-      <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>本日 15:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>残りわずか</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>満員</t>
+        </is>
+      </c>
       <c r="R4" s="5" t="inlineStr">
         <is>
-          <t>清楚系;美脚</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
+          <t>超絶美女;高身長;高リピート率;大人の魅力</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>x;zero2;relaxi;insta</t>
+        </is>
+      </c>
       <c r="T4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>あやか</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>18:00〜</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr"/>
+      <c r="N5" s="5" t="inlineStr"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>本日 18:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr"/>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>妖艶;モデル系;美脚;テク抜群</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>fgn;blue;zero2</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>みなみ</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>17:00〜</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="inlineStr"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>本日 17:00〜23:00</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr"/>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>新人;ロリ系;純粋;甘え上手</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
+        <is>
+          <t>zero2;relaxi</t>
+        </is>
+      </c>
+      <c r="T6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>れな</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>19:30〜</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>出勤</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>本日 19:30〜翌4:00</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr"/>
+      <c r="Q7" s="5" t="inlineStr">
+        <is>
+          <t>残りわずか</t>
+        </is>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>お姉様系;色白;癒やし;包容力</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>fgn;zero2;relaxi</t>
+        </is>
+      </c>
+      <c r="T7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>ゆい</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>✖️</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr"/>
+      <c r="N8" s="5" t="inlineStr"/>
+      <c r="O8" s="5" t="inlineStr"/>
+      <c r="P8" s="5" t="inlineStr"/>
+      <c r="Q8" s="5" t="inlineStr"/>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>清楚;美肌;スレンダー;笑顔</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>zero2</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>まりな</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>20:00〜</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr"/>
+      <c r="N9" s="5" t="inlineStr"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>本日 20:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr"/>
+      <c r="Q9" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>大人可愛い;グラマー;小顔;上品</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>fgn;blue;relaxi</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>ちなつ</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>14:00〜</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>AJ</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>はい</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="inlineStr"/>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>本日 14:00〜22:00</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr"/>
+      <c r="Q10" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>未経験;清純;小柄;一生懸命</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr">
+        <is>
+          <t>zero2;relaxi</t>
+        </is>
+      </c>
+      <c r="T10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>さき</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>在籍</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>21:00〜</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>diamond</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>◆</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr"/>
+      <c r="N11" s="5" t="inlineStr"/>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>本日 21:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr"/>
+      <c r="Q11" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>妖艶美人;高身長;美乳;テクニシャン</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>fgn;zero2;insta</t>
+        </is>
+      </c>
+      <c r="T11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1133,7 +1770,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>キー(自動)</t>
         </is>
@@ -1180,7 +1817,7 @@
           <t>確定</t>
         </is>
       </c>
-      <c r="I2" s="8">
+      <c r="I2" s="14">
         <f>IF($D2="","",$D2&amp;"|"&amp;$B2)</f>
         <v/>
       </c>
@@ -1203,17 +1840,17 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>ゆな</t>
+          <t>花恋</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>15:00〜23:00</t>
+          <t>16:00〜翌3:00</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>満員</t>
+          <t>空きあり</t>
         </is>
       </c>
       <c r="G3" s="6" t="inlineStr">
@@ -1226,7 +1863,7 @@
           <t>確定</t>
         </is>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="14">
         <f>IF($D3="","",$D3&amp;"|"&amp;$B3)</f>
         <v/>
       </c>
@@ -1234,1221 +1871,3013 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>9/16(水)</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>あやか</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>18:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I4" s="14">
+        <f>IF($D4="","",$D4&amp;"|"&amp;$B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>9/16(水)</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>れな</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>19:30〜翌4:00</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>残りわずか</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I5" s="14">
+        <f>IF($D5="","",$D5&amp;"|"&amp;$B5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/16</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>9/16(水)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>さき</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>21:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I6" s="14">
+        <f>IF($D6="","",$D6&amp;"|"&amp;$B6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
           <t>2026/9/17</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>9/17(木)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>亀戸</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>花恋</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>16:00〜翌3:00</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I7" s="14">
+        <f>IF($D7="","",$D7&amp;"|"&amp;$B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/17</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>9/17(木)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>まりな</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>20:00〜翌5:00</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I8" s="14">
+        <f>IF($D8="","",$D8&amp;"|"&amp;$B8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/17</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>9/17(木)</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>ちなつ</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>14:00〜22:00</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>申請中</t>
+        </is>
+      </c>
+      <c r="I9" s="14">
+        <f>IF($D9="","",$D9&amp;"|"&amp;$B9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/18</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>9/18(金)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>みお</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>18:00〜翌2:00</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>13:00〜翌2:00</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>空きあり</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>○</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>申請中</t>
-        </is>
-      </c>
-      <c r="I4" s="8">
-        <f>IF($D4="","",$D4&amp;"|"&amp;$B4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="I5" s="8">
-        <f>IF($D5="","",$D5&amp;"|"&amp;$B5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="I6" s="8">
-        <f>IF($D6="","",$D6&amp;"|"&amp;$B6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="I7" s="8">
-        <f>IF($D7="","",$D7&amp;"|"&amp;$B7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="I8" s="8">
-        <f>IF($D8="","",$D8&amp;"|"&amp;$B8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="I9" s="8">
-        <f>IF($D9="","",$D9&amp;"|"&amp;$B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="I10" s="8">
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I10" s="14">
         <f>IF($D10="","",$D10&amp;"|"&amp;$B10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="I11" s="8">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026/9/18</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>9/18(金)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>亀戸</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>みなみ</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>17:00〜23:00</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>空きあり</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>確定</t>
+        </is>
+      </c>
+      <c r="I11" s="14">
         <f>IF($D11="","",$D11&amp;"|"&amp;$B11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="I12" s="8">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="14">
         <f>IF($D12="","",$D12&amp;"|"&amp;$B12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="8">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="14">
         <f>IF($D13="","",$D13&amp;"|"&amp;$B13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="I14" s="8">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="14">
         <f>IF($D14="","",$D14&amp;"|"&amp;$B14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="I15" s="8">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="14">
         <f>IF($D15="","",$D15&amp;"|"&amp;$B15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="I16" s="8">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="14">
         <f>IF($D16="","",$D16&amp;"|"&amp;$B16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="I17" s="8">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="14">
         <f>IF($D17="","",$D17&amp;"|"&amp;$B17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="I18" s="8">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="14">
         <f>IF($D18="","",$D18&amp;"|"&amp;$B18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="I19" s="8">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="14">
         <f>IF($D19="","",$D19&amp;"|"&amp;$B19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="I20" s="8">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="14">
         <f>IF($D20="","",$D20&amp;"|"&amp;$B20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="I21" s="8">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="14">
         <f>IF($D21="","",$D21&amp;"|"&amp;$B21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="I22" s="8">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="14">
         <f>IF($D22="","",$D22&amp;"|"&amp;$B22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="I23" s="8">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="14">
         <f>IF($D23="","",$D23&amp;"|"&amp;$B23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="I24" s="8">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="14">
         <f>IF($D24="","",$D24&amp;"|"&amp;$B24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="I25" s="8">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+      <c r="G25" s="15" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="14">
         <f>IF($D25="","",$D25&amp;"|"&amp;$B25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="I26" s="8">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="15" t="n"/>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="14">
         <f>IF($D26="","",$D26&amp;"|"&amp;$B26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="I27" s="8">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="15" t="n"/>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="14">
         <f>IF($D27="","",$D27&amp;"|"&amp;$B27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="I28" s="8">
+      <c r="A28" s="15" t="n"/>
+      <c r="B28" s="15" t="n"/>
+      <c r="C28" s="15" t="n"/>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="14">
         <f>IF($D28="","",$D28&amp;"|"&amp;$B28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="I29" s="8">
+      <c r="A29" s="15" t="n"/>
+      <c r="B29" s="15" t="n"/>
+      <c r="C29" s="15" t="n"/>
+      <c r="D29" s="15" t="n"/>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="15" t="n"/>
+      <c r="G29" s="15" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="14">
         <f>IF($D29="","",$D29&amp;"|"&amp;$B29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="I30" s="8">
+      <c r="A30" s="15" t="n"/>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="15" t="n"/>
+      <c r="D30" s="15" t="n"/>
+      <c r="E30" s="15" t="n"/>
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="15" t="n"/>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="14">
         <f>IF($D30="","",$D30&amp;"|"&amp;$B30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="I31" s="8">
+      <c r="A31" s="15" t="n"/>
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="15" t="n"/>
+      <c r="D31" s="15" t="n"/>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="15" t="n"/>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="14">
         <f>IF($D31="","",$D31&amp;"|"&amp;$B31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="I32" s="8">
+      <c r="A32" s="15" t="n"/>
+      <c r="B32" s="15" t="n"/>
+      <c r="C32" s="15" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="15" t="n"/>
+      <c r="F32" s="15" t="n"/>
+      <c r="G32" s="15" t="n"/>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="14">
         <f>IF($D32="","",$D32&amp;"|"&amp;$B32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="I33" s="8">
+      <c r="A33" s="15" t="n"/>
+      <c r="B33" s="15" t="n"/>
+      <c r="C33" s="15" t="n"/>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="15" t="n"/>
+      <c r="G33" s="15" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="14">
         <f>IF($D33="","",$D33&amp;"|"&amp;$B33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="I34" s="8">
+      <c r="A34" s="15" t="n"/>
+      <c r="B34" s="15" t="n"/>
+      <c r="C34" s="15" t="n"/>
+      <c r="D34" s="15" t="n"/>
+      <c r="E34" s="15" t="n"/>
+      <c r="F34" s="15" t="n"/>
+      <c r="G34" s="15" t="n"/>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="14">
         <f>IF($D34="","",$D34&amp;"|"&amp;$B34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="I35" s="8">
+      <c r="A35" s="15" t="n"/>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="15" t="n"/>
+      <c r="D35" s="15" t="n"/>
+      <c r="E35" s="15" t="n"/>
+      <c r="F35" s="15" t="n"/>
+      <c r="G35" s="15" t="n"/>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="14">
         <f>IF($D35="","",$D35&amp;"|"&amp;$B35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="I36" s="8">
+      <c r="A36" s="15" t="n"/>
+      <c r="B36" s="15" t="n"/>
+      <c r="C36" s="15" t="n"/>
+      <c r="D36" s="15" t="n"/>
+      <c r="E36" s="15" t="n"/>
+      <c r="F36" s="15" t="n"/>
+      <c r="G36" s="15" t="n"/>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="14">
         <f>IF($D36="","",$D36&amp;"|"&amp;$B36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="I37" s="8">
+      <c r="A37" s="15" t="n"/>
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="15" t="n"/>
+      <c r="D37" s="15" t="n"/>
+      <c r="E37" s="15" t="n"/>
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="15" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="14">
         <f>IF($D37="","",$D37&amp;"|"&amp;$B37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="I38" s="8">
+      <c r="A38" s="15" t="n"/>
+      <c r="B38" s="15" t="n"/>
+      <c r="C38" s="15" t="n"/>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
+      <c r="F38" s="15" t="n"/>
+      <c r="G38" s="15" t="n"/>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="14">
         <f>IF($D38="","",$D38&amp;"|"&amp;$B38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="I39" s="8">
+      <c r="A39" s="15" t="n"/>
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="15" t="n"/>
+      <c r="D39" s="15" t="n"/>
+      <c r="E39" s="15" t="n"/>
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="15" t="n"/>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="14">
         <f>IF($D39="","",$D39&amp;"|"&amp;$B39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="I40" s="8">
+      <c r="A40" s="15" t="n"/>
+      <c r="B40" s="15" t="n"/>
+      <c r="C40" s="15" t="n"/>
+      <c r="D40" s="15" t="n"/>
+      <c r="E40" s="15" t="n"/>
+      <c r="F40" s="15" t="n"/>
+      <c r="G40" s="15" t="n"/>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="14">
         <f>IF($D40="","",$D40&amp;"|"&amp;$B40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="I41" s="8">
+      <c r="A41" s="15" t="n"/>
+      <c r="B41" s="15" t="n"/>
+      <c r="C41" s="15" t="n"/>
+      <c r="D41" s="15" t="n"/>
+      <c r="E41" s="15" t="n"/>
+      <c r="F41" s="15" t="n"/>
+      <c r="G41" s="15" t="n"/>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="14">
         <f>IF($D41="","",$D41&amp;"|"&amp;$B41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="I42" s="8">
+      <c r="A42" s="15" t="n"/>
+      <c r="B42" s="15" t="n"/>
+      <c r="C42" s="15" t="n"/>
+      <c r="D42" s="15" t="n"/>
+      <c r="E42" s="15" t="n"/>
+      <c r="F42" s="15" t="n"/>
+      <c r="G42" s="15" t="n"/>
+      <c r="H42" s="15" t="n"/>
+      <c r="I42" s="14">
         <f>IF($D42="","",$D42&amp;"|"&amp;$B42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="I43" s="8">
+      <c r="A43" s="15" t="n"/>
+      <c r="B43" s="15" t="n"/>
+      <c r="C43" s="15" t="n"/>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
+      <c r="F43" s="15" t="n"/>
+      <c r="G43" s="15" t="n"/>
+      <c r="H43" s="15" t="n"/>
+      <c r="I43" s="14">
         <f>IF($D43="","",$D43&amp;"|"&amp;$B43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="I44" s="8">
+      <c r="A44" s="15" t="n"/>
+      <c r="B44" s="15" t="n"/>
+      <c r="C44" s="15" t="n"/>
+      <c r="D44" s="15" t="n"/>
+      <c r="E44" s="15" t="n"/>
+      <c r="F44" s="15" t="n"/>
+      <c r="G44" s="15" t="n"/>
+      <c r="H44" s="15" t="n"/>
+      <c r="I44" s="14">
         <f>IF($D44="","",$D44&amp;"|"&amp;$B44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="I45" s="8">
+      <c r="A45" s="15" t="n"/>
+      <c r="B45" s="15" t="n"/>
+      <c r="C45" s="15" t="n"/>
+      <c r="D45" s="15" t="n"/>
+      <c r="E45" s="15" t="n"/>
+      <c r="F45" s="15" t="n"/>
+      <c r="G45" s="15" t="n"/>
+      <c r="H45" s="15" t="n"/>
+      <c r="I45" s="14">
         <f>IF($D45="","",$D45&amp;"|"&amp;$B45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="I46" s="8">
+      <c r="A46" s="15" t="n"/>
+      <c r="B46" s="15" t="n"/>
+      <c r="C46" s="15" t="n"/>
+      <c r="D46" s="15" t="n"/>
+      <c r="E46" s="15" t="n"/>
+      <c r="F46" s="15" t="n"/>
+      <c r="G46" s="15" t="n"/>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="14">
         <f>IF($D46="","",$D46&amp;"|"&amp;$B46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="I47" s="8">
+      <c r="A47" s="15" t="n"/>
+      <c r="B47" s="15" t="n"/>
+      <c r="C47" s="15" t="n"/>
+      <c r="D47" s="15" t="n"/>
+      <c r="E47" s="15" t="n"/>
+      <c r="F47" s="15" t="n"/>
+      <c r="G47" s="15" t="n"/>
+      <c r="H47" s="15" t="n"/>
+      <c r="I47" s="14">
         <f>IF($D47="","",$D47&amp;"|"&amp;$B47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="I48" s="8">
+      <c r="A48" s="15" t="n"/>
+      <c r="B48" s="15" t="n"/>
+      <c r="C48" s="15" t="n"/>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
+      <c r="F48" s="15" t="n"/>
+      <c r="G48" s="15" t="n"/>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="14">
         <f>IF($D48="","",$D48&amp;"|"&amp;$B48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="I49" s="8">
+      <c r="A49" s="15" t="n"/>
+      <c r="B49" s="15" t="n"/>
+      <c r="C49" s="15" t="n"/>
+      <c r="D49" s="15" t="n"/>
+      <c r="E49" s="15" t="n"/>
+      <c r="F49" s="15" t="n"/>
+      <c r="G49" s="15" t="n"/>
+      <c r="H49" s="15" t="n"/>
+      <c r="I49" s="14">
         <f>IF($D49="","",$D49&amp;"|"&amp;$B49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="I50" s="8">
+      <c r="A50" s="15" t="n"/>
+      <c r="B50" s="15" t="n"/>
+      <c r="C50" s="15" t="n"/>
+      <c r="D50" s="15" t="n"/>
+      <c r="E50" s="15" t="n"/>
+      <c r="F50" s="15" t="n"/>
+      <c r="G50" s="15" t="n"/>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="14">
         <f>IF($D50="","",$D50&amp;"|"&amp;$B50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="I51" s="8">
+      <c r="A51" s="15" t="n"/>
+      <c r="B51" s="15" t="n"/>
+      <c r="C51" s="15" t="n"/>
+      <c r="D51" s="15" t="n"/>
+      <c r="E51" s="15" t="n"/>
+      <c r="F51" s="15" t="n"/>
+      <c r="G51" s="15" t="n"/>
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="14">
         <f>IF($D51="","",$D51&amp;"|"&amp;$B51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="I52" s="8">
+      <c r="A52" s="15" t="n"/>
+      <c r="B52" s="15" t="n"/>
+      <c r="C52" s="15" t="n"/>
+      <c r="D52" s="15" t="n"/>
+      <c r="E52" s="15" t="n"/>
+      <c r="F52" s="15" t="n"/>
+      <c r="G52" s="15" t="n"/>
+      <c r="H52" s="15" t="n"/>
+      <c r="I52" s="14">
         <f>IF($D52="","",$D52&amp;"|"&amp;$B52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="I53" s="8">
+      <c r="A53" s="15" t="n"/>
+      <c r="B53" s="15" t="n"/>
+      <c r="C53" s="15" t="n"/>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
+      <c r="F53" s="15" t="n"/>
+      <c r="G53" s="15" t="n"/>
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="14">
         <f>IF($D53="","",$D53&amp;"|"&amp;$B53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="I54" s="8">
+      <c r="A54" s="15" t="n"/>
+      <c r="B54" s="15" t="n"/>
+      <c r="C54" s="15" t="n"/>
+      <c r="D54" s="15" t="n"/>
+      <c r="E54" s="15" t="n"/>
+      <c r="F54" s="15" t="n"/>
+      <c r="G54" s="15" t="n"/>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="14">
         <f>IF($D54="","",$D54&amp;"|"&amp;$B54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="I55" s="8">
+      <c r="A55" s="15" t="n"/>
+      <c r="B55" s="15" t="n"/>
+      <c r="C55" s="15" t="n"/>
+      <c r="D55" s="15" t="n"/>
+      <c r="E55" s="15" t="n"/>
+      <c r="F55" s="15" t="n"/>
+      <c r="G55" s="15" t="n"/>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="14">
         <f>IF($D55="","",$D55&amp;"|"&amp;$B55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="I56" s="8">
+      <c r="A56" s="15" t="n"/>
+      <c r="B56" s="15" t="n"/>
+      <c r="C56" s="15" t="n"/>
+      <c r="D56" s="15" t="n"/>
+      <c r="E56" s="15" t="n"/>
+      <c r="F56" s="15" t="n"/>
+      <c r="G56" s="15" t="n"/>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="14">
         <f>IF($D56="","",$D56&amp;"|"&amp;$B56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="I57" s="8">
+      <c r="A57" s="15" t="n"/>
+      <c r="B57" s="15" t="n"/>
+      <c r="C57" s="15" t="n"/>
+      <c r="D57" s="15" t="n"/>
+      <c r="E57" s="15" t="n"/>
+      <c r="F57" s="15" t="n"/>
+      <c r="G57" s="15" t="n"/>
+      <c r="H57" s="15" t="n"/>
+      <c r="I57" s="14">
         <f>IF($D57="","",$D57&amp;"|"&amp;$B57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="I58" s="8">
+      <c r="A58" s="15" t="n"/>
+      <c r="B58" s="15" t="n"/>
+      <c r="C58" s="15" t="n"/>
+      <c r="D58" s="15" t="n"/>
+      <c r="E58" s="15" t="n"/>
+      <c r="F58" s="15" t="n"/>
+      <c r="G58" s="15" t="n"/>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="14">
         <f>IF($D58="","",$D58&amp;"|"&amp;$B58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="I59" s="8">
+      <c r="A59" s="15" t="n"/>
+      <c r="B59" s="15" t="n"/>
+      <c r="C59" s="15" t="n"/>
+      <c r="D59" s="15" t="n"/>
+      <c r="E59" s="15" t="n"/>
+      <c r="F59" s="15" t="n"/>
+      <c r="G59" s="15" t="n"/>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="14">
         <f>IF($D59="","",$D59&amp;"|"&amp;$B59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="I60" s="8">
+      <c r="A60" s="15" t="n"/>
+      <c r="B60" s="15" t="n"/>
+      <c r="C60" s="15" t="n"/>
+      <c r="D60" s="15" t="n"/>
+      <c r="E60" s="15" t="n"/>
+      <c r="F60" s="15" t="n"/>
+      <c r="G60" s="15" t="n"/>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="14">
         <f>IF($D60="","",$D60&amp;"|"&amp;$B60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="I61" s="8">
+      <c r="A61" s="15" t="n"/>
+      <c r="B61" s="15" t="n"/>
+      <c r="C61" s="15" t="n"/>
+      <c r="D61" s="15" t="n"/>
+      <c r="E61" s="15" t="n"/>
+      <c r="F61" s="15" t="n"/>
+      <c r="G61" s="15" t="n"/>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="14">
         <f>IF($D61="","",$D61&amp;"|"&amp;$B61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="I62" s="8">
+      <c r="A62" s="15" t="n"/>
+      <c r="B62" s="15" t="n"/>
+      <c r="C62" s="15" t="n"/>
+      <c r="D62" s="15" t="n"/>
+      <c r="E62" s="15" t="n"/>
+      <c r="F62" s="15" t="n"/>
+      <c r="G62" s="15" t="n"/>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="14">
         <f>IF($D62="","",$D62&amp;"|"&amp;$B62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="I63" s="8">
+      <c r="A63" s="15" t="n"/>
+      <c r="B63" s="15" t="n"/>
+      <c r="C63" s="15" t="n"/>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
+      <c r="F63" s="15" t="n"/>
+      <c r="G63" s="15" t="n"/>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="14">
         <f>IF($D63="","",$D63&amp;"|"&amp;$B63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="I64" s="8">
+      <c r="A64" s="15" t="n"/>
+      <c r="B64" s="15" t="n"/>
+      <c r="C64" s="15" t="n"/>
+      <c r="D64" s="15" t="n"/>
+      <c r="E64" s="15" t="n"/>
+      <c r="F64" s="15" t="n"/>
+      <c r="G64" s="15" t="n"/>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="14">
         <f>IF($D64="","",$D64&amp;"|"&amp;$B64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="I65" s="8">
+      <c r="A65" s="15" t="n"/>
+      <c r="B65" s="15" t="n"/>
+      <c r="C65" s="15" t="n"/>
+      <c r="D65" s="15" t="n"/>
+      <c r="E65" s="15" t="n"/>
+      <c r="F65" s="15" t="n"/>
+      <c r="G65" s="15" t="n"/>
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="14">
         <f>IF($D65="","",$D65&amp;"|"&amp;$B65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="I66" s="8">
+      <c r="A66" s="15" t="n"/>
+      <c r="B66" s="15" t="n"/>
+      <c r="C66" s="15" t="n"/>
+      <c r="D66" s="15" t="n"/>
+      <c r="E66" s="15" t="n"/>
+      <c r="F66" s="15" t="n"/>
+      <c r="G66" s="15" t="n"/>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="14">
         <f>IF($D66="","",$D66&amp;"|"&amp;$B66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="I67" s="8">
+      <c r="A67" s="15" t="n"/>
+      <c r="B67" s="15" t="n"/>
+      <c r="C67" s="15" t="n"/>
+      <c r="D67" s="15" t="n"/>
+      <c r="E67" s="15" t="n"/>
+      <c r="F67" s="15" t="n"/>
+      <c r="G67" s="15" t="n"/>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="14">
         <f>IF($D67="","",$D67&amp;"|"&amp;$B67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="I68" s="8">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="15" t="n"/>
+      <c r="C68" s="15" t="n"/>
+      <c r="D68" s="15" t="n"/>
+      <c r="E68" s="15" t="n"/>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="15" t="n"/>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="14">
         <f>IF($D68="","",$D68&amp;"|"&amp;$B68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="I69" s="8">
+      <c r="A69" s="15" t="n"/>
+      <c r="B69" s="15" t="n"/>
+      <c r="C69" s="15" t="n"/>
+      <c r="D69" s="15" t="n"/>
+      <c r="E69" s="15" t="n"/>
+      <c r="F69" s="15" t="n"/>
+      <c r="G69" s="15" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="14">
         <f>IF($D69="","",$D69&amp;"|"&amp;$B69)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="I70" s="8">
+      <c r="A70" s="15" t="n"/>
+      <c r="B70" s="15" t="n"/>
+      <c r="C70" s="15" t="n"/>
+      <c r="D70" s="15" t="n"/>
+      <c r="E70" s="15" t="n"/>
+      <c r="F70" s="15" t="n"/>
+      <c r="G70" s="15" t="n"/>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="14">
         <f>IF($D70="","",$D70&amp;"|"&amp;$B70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="I71" s="8">
+      <c r="A71" s="15" t="n"/>
+      <c r="B71" s="15" t="n"/>
+      <c r="C71" s="15" t="n"/>
+      <c r="D71" s="15" t="n"/>
+      <c r="E71" s="15" t="n"/>
+      <c r="F71" s="15" t="n"/>
+      <c r="G71" s="15" t="n"/>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="14">
         <f>IF($D71="","",$D71&amp;"|"&amp;$B71)</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="I72" s="8">
+      <c r="A72" s="15" t="n"/>
+      <c r="B72" s="15" t="n"/>
+      <c r="C72" s="15" t="n"/>
+      <c r="D72" s="15" t="n"/>
+      <c r="E72" s="15" t="n"/>
+      <c r="F72" s="15" t="n"/>
+      <c r="G72" s="15" t="n"/>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="14">
         <f>IF($D72="","",$D72&amp;"|"&amp;$B72)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="I73" s="8">
+      <c r="A73" s="15" t="n"/>
+      <c r="B73" s="15" t="n"/>
+      <c r="C73" s="15" t="n"/>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
+      <c r="F73" s="15" t="n"/>
+      <c r="G73" s="15" t="n"/>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="14">
         <f>IF($D73="","",$D73&amp;"|"&amp;$B73)</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="I74" s="8">
+      <c r="A74" s="15" t="n"/>
+      <c r="B74" s="15" t="n"/>
+      <c r="C74" s="15" t="n"/>
+      <c r="D74" s="15" t="n"/>
+      <c r="E74" s="15" t="n"/>
+      <c r="F74" s="15" t="n"/>
+      <c r="G74" s="15" t="n"/>
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="14">
         <f>IF($D74="","",$D74&amp;"|"&amp;$B74)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="I75" s="8">
+      <c r="A75" s="15" t="n"/>
+      <c r="B75" s="15" t="n"/>
+      <c r="C75" s="15" t="n"/>
+      <c r="D75" s="15" t="n"/>
+      <c r="E75" s="15" t="n"/>
+      <c r="F75" s="15" t="n"/>
+      <c r="G75" s="15" t="n"/>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="14">
         <f>IF($D75="","",$D75&amp;"|"&amp;$B75)</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="I76" s="8">
+      <c r="A76" s="15" t="n"/>
+      <c r="B76" s="15" t="n"/>
+      <c r="C76" s="15" t="n"/>
+      <c r="D76" s="15" t="n"/>
+      <c r="E76" s="15" t="n"/>
+      <c r="F76" s="15" t="n"/>
+      <c r="G76" s="15" t="n"/>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="14">
         <f>IF($D76="","",$D76&amp;"|"&amp;$B76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="I77" s="8">
+      <c r="A77" s="15" t="n"/>
+      <c r="B77" s="15" t="n"/>
+      <c r="C77" s="15" t="n"/>
+      <c r="D77" s="15" t="n"/>
+      <c r="E77" s="15" t="n"/>
+      <c r="F77" s="15" t="n"/>
+      <c r="G77" s="15" t="n"/>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="14">
         <f>IF($D77="","",$D77&amp;"|"&amp;$B77)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="I78" s="8">
+      <c r="A78" s="15" t="n"/>
+      <c r="B78" s="15" t="n"/>
+      <c r="C78" s="15" t="n"/>
+      <c r="D78" s="15" t="n"/>
+      <c r="E78" s="15" t="n"/>
+      <c r="F78" s="15" t="n"/>
+      <c r="G78" s="15" t="n"/>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="14">
         <f>IF($D78="","",$D78&amp;"|"&amp;$B78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="I79" s="8">
+      <c r="A79" s="15" t="n"/>
+      <c r="B79" s="15" t="n"/>
+      <c r="C79" s="15" t="n"/>
+      <c r="D79" s="15" t="n"/>
+      <c r="E79" s="15" t="n"/>
+      <c r="F79" s="15" t="n"/>
+      <c r="G79" s="15" t="n"/>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="14">
         <f>IF($D79="","",$D79&amp;"|"&amp;$B79)</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="I80" s="8">
+      <c r="A80" s="15" t="n"/>
+      <c r="B80" s="15" t="n"/>
+      <c r="C80" s="15" t="n"/>
+      <c r="D80" s="15" t="n"/>
+      <c r="E80" s="15" t="n"/>
+      <c r="F80" s="15" t="n"/>
+      <c r="G80" s="15" t="n"/>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="14">
         <f>IF($D80="","",$D80&amp;"|"&amp;$B80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="I81" s="8">
+      <c r="A81" s="15" t="n"/>
+      <c r="B81" s="15" t="n"/>
+      <c r="C81" s="15" t="n"/>
+      <c r="D81" s="15" t="n"/>
+      <c r="E81" s="15" t="n"/>
+      <c r="F81" s="15" t="n"/>
+      <c r="G81" s="15" t="n"/>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="14">
         <f>IF($D81="","",$D81&amp;"|"&amp;$B81)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="I82" s="8">
+      <c r="A82" s="15" t="n"/>
+      <c r="B82" s="15" t="n"/>
+      <c r="C82" s="15" t="n"/>
+      <c r="D82" s="15" t="n"/>
+      <c r="E82" s="15" t="n"/>
+      <c r="F82" s="15" t="n"/>
+      <c r="G82" s="15" t="n"/>
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="14">
         <f>IF($D82="","",$D82&amp;"|"&amp;$B82)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="I83" s="8">
+      <c r="A83" s="15" t="n"/>
+      <c r="B83" s="15" t="n"/>
+      <c r="C83" s="15" t="n"/>
+      <c r="D83" s="15" t="n"/>
+      <c r="E83" s="15" t="n"/>
+      <c r="F83" s="15" t="n"/>
+      <c r="G83" s="15" t="n"/>
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="14">
         <f>IF($D83="","",$D83&amp;"|"&amp;$B83)</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="I84" s="8">
+      <c r="A84" s="15" t="n"/>
+      <c r="B84" s="15" t="n"/>
+      <c r="C84" s="15" t="n"/>
+      <c r="D84" s="15" t="n"/>
+      <c r="E84" s="15" t="n"/>
+      <c r="F84" s="15" t="n"/>
+      <c r="G84" s="15" t="n"/>
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="14">
         <f>IF($D84="","",$D84&amp;"|"&amp;$B84)</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="I85" s="8">
+      <c r="A85" s="15" t="n"/>
+      <c r="B85" s="15" t="n"/>
+      <c r="C85" s="15" t="n"/>
+      <c r="D85" s="15" t="n"/>
+      <c r="E85" s="15" t="n"/>
+      <c r="F85" s="15" t="n"/>
+      <c r="G85" s="15" t="n"/>
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="14">
         <f>IF($D85="","",$D85&amp;"|"&amp;$B85)</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="I86" s="8">
+      <c r="A86" s="15" t="n"/>
+      <c r="B86" s="15" t="n"/>
+      <c r="C86" s="15" t="n"/>
+      <c r="D86" s="15" t="n"/>
+      <c r="E86" s="15" t="n"/>
+      <c r="F86" s="15" t="n"/>
+      <c r="G86" s="15" t="n"/>
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="14">
         <f>IF($D86="","",$D86&amp;"|"&amp;$B86)</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="I87" s="8">
+      <c r="A87" s="15" t="n"/>
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="15" t="n"/>
+      <c r="D87" s="15" t="n"/>
+      <c r="E87" s="15" t="n"/>
+      <c r="F87" s="15" t="n"/>
+      <c r="G87" s="15" t="n"/>
+      <c r="H87" s="15" t="n"/>
+      <c r="I87" s="14">
         <f>IF($D87="","",$D87&amp;"|"&amp;$B87)</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="I88" s="8">
+      <c r="A88" s="15" t="n"/>
+      <c r="B88" s="15" t="n"/>
+      <c r="C88" s="15" t="n"/>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
+      <c r="F88" s="15" t="n"/>
+      <c r="G88" s="15" t="n"/>
+      <c r="H88" s="15" t="n"/>
+      <c r="I88" s="14">
         <f>IF($D88="","",$D88&amp;"|"&amp;$B88)</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="I89" s="8">
+      <c r="A89" s="15" t="n"/>
+      <c r="B89" s="15" t="n"/>
+      <c r="C89" s="15" t="n"/>
+      <c r="D89" s="15" t="n"/>
+      <c r="E89" s="15" t="n"/>
+      <c r="F89" s="15" t="n"/>
+      <c r="G89" s="15" t="n"/>
+      <c r="H89" s="15" t="n"/>
+      <c r="I89" s="14">
         <f>IF($D89="","",$D89&amp;"|"&amp;$B89)</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="I90" s="8">
+      <c r="A90" s="15" t="n"/>
+      <c r="B90" s="15" t="n"/>
+      <c r="C90" s="15" t="n"/>
+      <c r="D90" s="15" t="n"/>
+      <c r="E90" s="15" t="n"/>
+      <c r="F90" s="15" t="n"/>
+      <c r="G90" s="15" t="n"/>
+      <c r="H90" s="15" t="n"/>
+      <c r="I90" s="14">
         <f>IF($D90="","",$D90&amp;"|"&amp;$B90)</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="I91" s="8">
+      <c r="A91" s="15" t="n"/>
+      <c r="B91" s="15" t="n"/>
+      <c r="C91" s="15" t="n"/>
+      <c r="D91" s="15" t="n"/>
+      <c r="E91" s="15" t="n"/>
+      <c r="F91" s="15" t="n"/>
+      <c r="G91" s="15" t="n"/>
+      <c r="H91" s="15" t="n"/>
+      <c r="I91" s="14">
         <f>IF($D91="","",$D91&amp;"|"&amp;$B91)</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="I92" s="8">
+      <c r="A92" s="15" t="n"/>
+      <c r="B92" s="15" t="n"/>
+      <c r="C92" s="15" t="n"/>
+      <c r="D92" s="15" t="n"/>
+      <c r="E92" s="15" t="n"/>
+      <c r="F92" s="15" t="n"/>
+      <c r="G92" s="15" t="n"/>
+      <c r="H92" s="15" t="n"/>
+      <c r="I92" s="14">
         <f>IF($D92="","",$D92&amp;"|"&amp;$B92)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="I93" s="8">
+      <c r="A93" s="15" t="n"/>
+      <c r="B93" s="15" t="n"/>
+      <c r="C93" s="15" t="n"/>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
+      <c r="F93" s="15" t="n"/>
+      <c r="G93" s="15" t="n"/>
+      <c r="H93" s="15" t="n"/>
+      <c r="I93" s="14">
         <f>IF($D93="","",$D93&amp;"|"&amp;$B93)</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="I94" s="8">
+      <c r="A94" s="15" t="n"/>
+      <c r="B94" s="15" t="n"/>
+      <c r="C94" s="15" t="n"/>
+      <c r="D94" s="15" t="n"/>
+      <c r="E94" s="15" t="n"/>
+      <c r="F94" s="15" t="n"/>
+      <c r="G94" s="15" t="n"/>
+      <c r="H94" s="15" t="n"/>
+      <c r="I94" s="14">
         <f>IF($D94="","",$D94&amp;"|"&amp;$B94)</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="I95" s="8">
+      <c r="A95" s="15" t="n"/>
+      <c r="B95" s="15" t="n"/>
+      <c r="C95" s="15" t="n"/>
+      <c r="D95" s="15" t="n"/>
+      <c r="E95" s="15" t="n"/>
+      <c r="F95" s="15" t="n"/>
+      <c r="G95" s="15" t="n"/>
+      <c r="H95" s="15" t="n"/>
+      <c r="I95" s="14">
         <f>IF($D95="","",$D95&amp;"|"&amp;$B95)</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="I96" s="8">
+      <c r="A96" s="15" t="n"/>
+      <c r="B96" s="15" t="n"/>
+      <c r="C96" s="15" t="n"/>
+      <c r="D96" s="15" t="n"/>
+      <c r="E96" s="15" t="n"/>
+      <c r="F96" s="15" t="n"/>
+      <c r="G96" s="15" t="n"/>
+      <c r="H96" s="15" t="n"/>
+      <c r="I96" s="14">
         <f>IF($D96="","",$D96&amp;"|"&amp;$B96)</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="I97" s="8">
+      <c r="A97" s="15" t="n"/>
+      <c r="B97" s="15" t="n"/>
+      <c r="C97" s="15" t="n"/>
+      <c r="D97" s="15" t="n"/>
+      <c r="E97" s="15" t="n"/>
+      <c r="F97" s="15" t="n"/>
+      <c r="G97" s="15" t="n"/>
+      <c r="H97" s="15" t="n"/>
+      <c r="I97" s="14">
         <f>IF($D97="","",$D97&amp;"|"&amp;$B97)</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="I98" s="8">
+      <c r="A98" s="15" t="n"/>
+      <c r="B98" s="15" t="n"/>
+      <c r="C98" s="15" t="n"/>
+      <c r="D98" s="15" t="n"/>
+      <c r="E98" s="15" t="n"/>
+      <c r="F98" s="15" t="n"/>
+      <c r="G98" s="15" t="n"/>
+      <c r="H98" s="15" t="n"/>
+      <c r="I98" s="14">
         <f>IF($D98="","",$D98&amp;"|"&amp;$B98)</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="I99" s="8">
+      <c r="A99" s="15" t="n"/>
+      <c r="B99" s="15" t="n"/>
+      <c r="C99" s="15" t="n"/>
+      <c r="D99" s="15" t="n"/>
+      <c r="E99" s="15" t="n"/>
+      <c r="F99" s="15" t="n"/>
+      <c r="G99" s="15" t="n"/>
+      <c r="H99" s="15" t="n"/>
+      <c r="I99" s="14">
         <f>IF($D99="","",$D99&amp;"|"&amp;$B99)</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="I100" s="8">
+      <c r="A100" s="15" t="n"/>
+      <c r="B100" s="15" t="n"/>
+      <c r="C100" s="15" t="n"/>
+      <c r="D100" s="15" t="n"/>
+      <c r="E100" s="15" t="n"/>
+      <c r="F100" s="15" t="n"/>
+      <c r="G100" s="15" t="n"/>
+      <c r="H100" s="15" t="n"/>
+      <c r="I100" s="14">
         <f>IF($D100="","",$D100&amp;"|"&amp;$B100)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="I101" s="8">
+      <c r="A101" s="15" t="n"/>
+      <c r="B101" s="15" t="n"/>
+      <c r="C101" s="15" t="n"/>
+      <c r="D101" s="15" t="n"/>
+      <c r="E101" s="15" t="n"/>
+      <c r="F101" s="15" t="n"/>
+      <c r="G101" s="15" t="n"/>
+      <c r="H101" s="15" t="n"/>
+      <c r="I101" s="14">
         <f>IF($D101="","",$D101&amp;"|"&amp;$B101)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="I102" s="8">
+      <c r="A102" s="15" t="n"/>
+      <c r="B102" s="15" t="n"/>
+      <c r="C102" s="15" t="n"/>
+      <c r="D102" s="15" t="n"/>
+      <c r="E102" s="15" t="n"/>
+      <c r="F102" s="15" t="n"/>
+      <c r="G102" s="15" t="n"/>
+      <c r="H102" s="15" t="n"/>
+      <c r="I102" s="14">
         <f>IF($D102="","",$D102&amp;"|"&amp;$B102)</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="I103" s="8">
+      <c r="A103" s="15" t="n"/>
+      <c r="B103" s="15" t="n"/>
+      <c r="C103" s="15" t="n"/>
+      <c r="D103" s="15" t="n"/>
+      <c r="E103" s="15" t="n"/>
+      <c r="F103" s="15" t="n"/>
+      <c r="G103" s="15" t="n"/>
+      <c r="H103" s="15" t="n"/>
+      <c r="I103" s="14">
         <f>IF($D103="","",$D103&amp;"|"&amp;$B103)</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="I104" s="8">
+      <c r="A104" s="15" t="n"/>
+      <c r="B104" s="15" t="n"/>
+      <c r="C104" s="15" t="n"/>
+      <c r="D104" s="15" t="n"/>
+      <c r="E104" s="15" t="n"/>
+      <c r="F104" s="15" t="n"/>
+      <c r="G104" s="15" t="n"/>
+      <c r="H104" s="15" t="n"/>
+      <c r="I104" s="14">
         <f>IF($D104="","",$D104&amp;"|"&amp;$B104)</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="I105" s="8">
+      <c r="A105" s="15" t="n"/>
+      <c r="B105" s="15" t="n"/>
+      <c r="C105" s="15" t="n"/>
+      <c r="D105" s="15" t="n"/>
+      <c r="E105" s="15" t="n"/>
+      <c r="F105" s="15" t="n"/>
+      <c r="G105" s="15" t="n"/>
+      <c r="H105" s="15" t="n"/>
+      <c r="I105" s="14">
         <f>IF($D105="","",$D105&amp;"|"&amp;$B105)</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="I106" s="8">
+      <c r="A106" s="15" t="n"/>
+      <c r="B106" s="15" t="n"/>
+      <c r="C106" s="15" t="n"/>
+      <c r="D106" s="15" t="n"/>
+      <c r="E106" s="15" t="n"/>
+      <c r="F106" s="15" t="n"/>
+      <c r="G106" s="15" t="n"/>
+      <c r="H106" s="15" t="n"/>
+      <c r="I106" s="14">
         <f>IF($D106="","",$D106&amp;"|"&amp;$B106)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="I107" s="8">
+      <c r="A107" s="15" t="n"/>
+      <c r="B107" s="15" t="n"/>
+      <c r="C107" s="15" t="n"/>
+      <c r="D107" s="15" t="n"/>
+      <c r="E107" s="15" t="n"/>
+      <c r="F107" s="15" t="n"/>
+      <c r="G107" s="15" t="n"/>
+      <c r="H107" s="15" t="n"/>
+      <c r="I107" s="14">
         <f>IF($D107="","",$D107&amp;"|"&amp;$B107)</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="I108" s="8">
+      <c r="A108" s="15" t="n"/>
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="15" t="n"/>
+      <c r="G108" s="15" t="n"/>
+      <c r="H108" s="15" t="n"/>
+      <c r="I108" s="14">
         <f>IF($D108="","",$D108&amp;"|"&amp;$B108)</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="I109" s="8">
+      <c r="A109" s="15" t="n"/>
+      <c r="B109" s="15" t="n"/>
+      <c r="C109" s="15" t="n"/>
+      <c r="D109" s="15" t="n"/>
+      <c r="E109" s="15" t="n"/>
+      <c r="F109" s="15" t="n"/>
+      <c r="G109" s="15" t="n"/>
+      <c r="H109" s="15" t="n"/>
+      <c r="I109" s="14">
         <f>IF($D109="","",$D109&amp;"|"&amp;$B109)</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="I110" s="8">
+      <c r="A110" s="15" t="n"/>
+      <c r="B110" s="15" t="n"/>
+      <c r="C110" s="15" t="n"/>
+      <c r="D110" s="15" t="n"/>
+      <c r="E110" s="15" t="n"/>
+      <c r="F110" s="15" t="n"/>
+      <c r="G110" s="15" t="n"/>
+      <c r="H110" s="15" t="n"/>
+      <c r="I110" s="14">
         <f>IF($D110="","",$D110&amp;"|"&amp;$B110)</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="I111" s="8">
+      <c r="A111" s="15" t="n"/>
+      <c r="B111" s="15" t="n"/>
+      <c r="C111" s="15" t="n"/>
+      <c r="D111" s="15" t="n"/>
+      <c r="E111" s="15" t="n"/>
+      <c r="F111" s="15" t="n"/>
+      <c r="G111" s="15" t="n"/>
+      <c r="H111" s="15" t="n"/>
+      <c r="I111" s="14">
         <f>IF($D111="","",$D111&amp;"|"&amp;$B111)</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="I112" s="8">
+      <c r="A112" s="15" t="n"/>
+      <c r="B112" s="15" t="n"/>
+      <c r="C112" s="15" t="n"/>
+      <c r="D112" s="15" t="n"/>
+      <c r="E112" s="15" t="n"/>
+      <c r="F112" s="15" t="n"/>
+      <c r="G112" s="15" t="n"/>
+      <c r="H112" s="15" t="n"/>
+      <c r="I112" s="14">
         <f>IF($D112="","",$D112&amp;"|"&amp;$B112)</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="I113" s="8">
+      <c r="A113" s="15" t="n"/>
+      <c r="B113" s="15" t="n"/>
+      <c r="C113" s="15" t="n"/>
+      <c r="D113" s="15" t="n"/>
+      <c r="E113" s="15" t="n"/>
+      <c r="F113" s="15" t="n"/>
+      <c r="G113" s="15" t="n"/>
+      <c r="H113" s="15" t="n"/>
+      <c r="I113" s="14">
         <f>IF($D113="","",$D113&amp;"|"&amp;$B113)</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="I114" s="8">
+      <c r="A114" s="15" t="n"/>
+      <c r="B114" s="15" t="n"/>
+      <c r="C114" s="15" t="n"/>
+      <c r="D114" s="15" t="n"/>
+      <c r="E114" s="15" t="n"/>
+      <c r="F114" s="15" t="n"/>
+      <c r="G114" s="15" t="n"/>
+      <c r="H114" s="15" t="n"/>
+      <c r="I114" s="14">
         <f>IF($D114="","",$D114&amp;"|"&amp;$B114)</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="I115" s="8">
+      <c r="A115" s="15" t="n"/>
+      <c r="B115" s="15" t="n"/>
+      <c r="C115" s="15" t="n"/>
+      <c r="D115" s="15" t="n"/>
+      <c r="E115" s="15" t="n"/>
+      <c r="F115" s="15" t="n"/>
+      <c r="G115" s="15" t="n"/>
+      <c r="H115" s="15" t="n"/>
+      <c r="I115" s="14">
         <f>IF($D115="","",$D115&amp;"|"&amp;$B115)</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="I116" s="8">
+      <c r="A116" s="15" t="n"/>
+      <c r="B116" s="15" t="n"/>
+      <c r="C116" s="15" t="n"/>
+      <c r="D116" s="15" t="n"/>
+      <c r="E116" s="15" t="n"/>
+      <c r="F116" s="15" t="n"/>
+      <c r="G116" s="15" t="n"/>
+      <c r="H116" s="15" t="n"/>
+      <c r="I116" s="14">
         <f>IF($D116="","",$D116&amp;"|"&amp;$B116)</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="I117" s="8">
+      <c r="A117" s="15" t="n"/>
+      <c r="B117" s="15" t="n"/>
+      <c r="C117" s="15" t="n"/>
+      <c r="D117" s="15" t="n"/>
+      <c r="E117" s="15" t="n"/>
+      <c r="F117" s="15" t="n"/>
+      <c r="G117" s="15" t="n"/>
+      <c r="H117" s="15" t="n"/>
+      <c r="I117" s="14">
         <f>IF($D117="","",$D117&amp;"|"&amp;$B117)</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="I118" s="8">
+      <c r="A118" s="15" t="n"/>
+      <c r="B118" s="15" t="n"/>
+      <c r="C118" s="15" t="n"/>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
+      <c r="F118" s="15" t="n"/>
+      <c r="G118" s="15" t="n"/>
+      <c r="H118" s="15" t="n"/>
+      <c r="I118" s="14">
         <f>IF($D118="","",$D118&amp;"|"&amp;$B118)</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="I119" s="8">
+      <c r="A119" s="15" t="n"/>
+      <c r="B119" s="15" t="n"/>
+      <c r="C119" s="15" t="n"/>
+      <c r="D119" s="15" t="n"/>
+      <c r="E119" s="15" t="n"/>
+      <c r="F119" s="15" t="n"/>
+      <c r="G119" s="15" t="n"/>
+      <c r="H119" s="15" t="n"/>
+      <c r="I119" s="14">
         <f>IF($D119="","",$D119&amp;"|"&amp;$B119)</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="I120" s="8">
+      <c r="A120" s="15" t="n"/>
+      <c r="B120" s="15" t="n"/>
+      <c r="C120" s="15" t="n"/>
+      <c r="D120" s="15" t="n"/>
+      <c r="E120" s="15" t="n"/>
+      <c r="F120" s="15" t="n"/>
+      <c r="G120" s="15" t="n"/>
+      <c r="H120" s="15" t="n"/>
+      <c r="I120" s="14">
         <f>IF($D120="","",$D120&amp;"|"&amp;$B120)</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="I121" s="8">
+      <c r="A121" s="15" t="n"/>
+      <c r="B121" s="15" t="n"/>
+      <c r="C121" s="15" t="n"/>
+      <c r="D121" s="15" t="n"/>
+      <c r="E121" s="15" t="n"/>
+      <c r="F121" s="15" t="n"/>
+      <c r="G121" s="15" t="n"/>
+      <c r="H121" s="15" t="n"/>
+      <c r="I121" s="14">
         <f>IF($D121="","",$D121&amp;"|"&amp;$B121)</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="I122" s="8">
+      <c r="A122" s="15" t="n"/>
+      <c r="B122" s="15" t="n"/>
+      <c r="C122" s="15" t="n"/>
+      <c r="D122" s="15" t="n"/>
+      <c r="E122" s="15" t="n"/>
+      <c r="F122" s="15" t="n"/>
+      <c r="G122" s="15" t="n"/>
+      <c r="H122" s="15" t="n"/>
+      <c r="I122" s="14">
         <f>IF($D122="","",$D122&amp;"|"&amp;$B122)</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="I123" s="8">
+      <c r="A123" s="15" t="n"/>
+      <c r="B123" s="15" t="n"/>
+      <c r="C123" s="15" t="n"/>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="n"/>
+      <c r="F123" s="15" t="n"/>
+      <c r="G123" s="15" t="n"/>
+      <c r="H123" s="15" t="n"/>
+      <c r="I123" s="14">
         <f>IF($D123="","",$D123&amp;"|"&amp;$B123)</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="I124" s="8">
+      <c r="A124" s="15" t="n"/>
+      <c r="B124" s="15" t="n"/>
+      <c r="C124" s="15" t="n"/>
+      <c r="D124" s="15" t="n"/>
+      <c r="E124" s="15" t="n"/>
+      <c r="F124" s="15" t="n"/>
+      <c r="G124" s="15" t="n"/>
+      <c r="H124" s="15" t="n"/>
+      <c r="I124" s="14">
         <f>IF($D124="","",$D124&amp;"|"&amp;$B124)</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="I125" s="8">
+      <c r="A125" s="15" t="n"/>
+      <c r="B125" s="15" t="n"/>
+      <c r="C125" s="15" t="n"/>
+      <c r="D125" s="15" t="n"/>
+      <c r="E125" s="15" t="n"/>
+      <c r="F125" s="15" t="n"/>
+      <c r="G125" s="15" t="n"/>
+      <c r="H125" s="15" t="n"/>
+      <c r="I125" s="14">
         <f>IF($D125="","",$D125&amp;"|"&amp;$B125)</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="I126" s="8">
+      <c r="A126" s="15" t="n"/>
+      <c r="B126" s="15" t="n"/>
+      <c r="C126" s="15" t="n"/>
+      <c r="D126" s="15" t="n"/>
+      <c r="E126" s="15" t="n"/>
+      <c r="F126" s="15" t="n"/>
+      <c r="G126" s="15" t="n"/>
+      <c r="H126" s="15" t="n"/>
+      <c r="I126" s="14">
         <f>IF($D126="","",$D126&amp;"|"&amp;$B126)</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="I127" s="8">
+      <c r="A127" s="15" t="n"/>
+      <c r="B127" s="15" t="n"/>
+      <c r="C127" s="15" t="n"/>
+      <c r="D127" s="15" t="n"/>
+      <c r="E127" s="15" t="n"/>
+      <c r="F127" s="15" t="n"/>
+      <c r="G127" s="15" t="n"/>
+      <c r="H127" s="15" t="n"/>
+      <c r="I127" s="14">
         <f>IF($D127="","",$D127&amp;"|"&amp;$B127)</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="I128" s="8">
+      <c r="A128" s="15" t="n"/>
+      <c r="B128" s="15" t="n"/>
+      <c r="C128" s="15" t="n"/>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
+      <c r="F128" s="15" t="n"/>
+      <c r="G128" s="15" t="n"/>
+      <c r="H128" s="15" t="n"/>
+      <c r="I128" s="14">
         <f>IF($D128="","",$D128&amp;"|"&amp;$B128)</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="I129" s="8">
+      <c r="A129" s="15" t="n"/>
+      <c r="B129" s="15" t="n"/>
+      <c r="C129" s="15" t="n"/>
+      <c r="D129" s="15" t="n"/>
+      <c r="E129" s="15" t="n"/>
+      <c r="F129" s="15" t="n"/>
+      <c r="G129" s="15" t="n"/>
+      <c r="H129" s="15" t="n"/>
+      <c r="I129" s="14">
         <f>IF($D129="","",$D129&amp;"|"&amp;$B129)</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="I130" s="8">
+      <c r="A130" s="15" t="n"/>
+      <c r="B130" s="15" t="n"/>
+      <c r="C130" s="15" t="n"/>
+      <c r="D130" s="15" t="n"/>
+      <c r="E130" s="15" t="n"/>
+      <c r="F130" s="15" t="n"/>
+      <c r="G130" s="15" t="n"/>
+      <c r="H130" s="15" t="n"/>
+      <c r="I130" s="14">
         <f>IF($D130="","",$D130&amp;"|"&amp;$B130)</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="I131" s="8">
+      <c r="A131" s="15" t="n"/>
+      <c r="B131" s="15" t="n"/>
+      <c r="C131" s="15" t="n"/>
+      <c r="D131" s="15" t="n"/>
+      <c r="E131" s="15" t="n"/>
+      <c r="F131" s="15" t="n"/>
+      <c r="G131" s="15" t="n"/>
+      <c r="H131" s="15" t="n"/>
+      <c r="I131" s="14">
         <f>IF($D131="","",$D131&amp;"|"&amp;$B131)</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="I132" s="8">
+      <c r="A132" s="15" t="n"/>
+      <c r="B132" s="15" t="n"/>
+      <c r="C132" s="15" t="n"/>
+      <c r="D132" s="15" t="n"/>
+      <c r="E132" s="15" t="n"/>
+      <c r="F132" s="15" t="n"/>
+      <c r="G132" s="15" t="n"/>
+      <c r="H132" s="15" t="n"/>
+      <c r="I132" s="14">
         <f>IF($D132="","",$D132&amp;"|"&amp;$B132)</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="I133" s="8">
+      <c r="A133" s="15" t="n"/>
+      <c r="B133" s="15" t="n"/>
+      <c r="C133" s="15" t="n"/>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
+      <c r="F133" s="15" t="n"/>
+      <c r="G133" s="15" t="n"/>
+      <c r="H133" s="15" t="n"/>
+      <c r="I133" s="14">
         <f>IF($D133="","",$D133&amp;"|"&amp;$B133)</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="I134" s="8">
+      <c r="A134" s="15" t="n"/>
+      <c r="B134" s="15" t="n"/>
+      <c r="C134" s="15" t="n"/>
+      <c r="D134" s="15" t="n"/>
+      <c r="E134" s="15" t="n"/>
+      <c r="F134" s="15" t="n"/>
+      <c r="G134" s="15" t="n"/>
+      <c r="H134" s="15" t="n"/>
+      <c r="I134" s="14">
         <f>IF($D134="","",$D134&amp;"|"&amp;$B134)</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="I135" s="8">
+      <c r="A135" s="15" t="n"/>
+      <c r="B135" s="15" t="n"/>
+      <c r="C135" s="15" t="n"/>
+      <c r="D135" s="15" t="n"/>
+      <c r="E135" s="15" t="n"/>
+      <c r="F135" s="15" t="n"/>
+      <c r="G135" s="15" t="n"/>
+      <c r="H135" s="15" t="n"/>
+      <c r="I135" s="14">
         <f>IF($D135="","",$D135&amp;"|"&amp;$B135)</f>
         <v/>
       </c>
     </row>
     <row r="136">
-      <c r="I136" s="8">
+      <c r="A136" s="15" t="n"/>
+      <c r="B136" s="15" t="n"/>
+      <c r="C136" s="15" t="n"/>
+      <c r="D136" s="15" t="n"/>
+      <c r="E136" s="15" t="n"/>
+      <c r="F136" s="15" t="n"/>
+      <c r="G136" s="15" t="n"/>
+      <c r="H136" s="15" t="n"/>
+      <c r="I136" s="14">
         <f>IF($D136="","",$D136&amp;"|"&amp;$B136)</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="I137" s="8">
+      <c r="A137" s="15" t="n"/>
+      <c r="B137" s="15" t="n"/>
+      <c r="C137" s="15" t="n"/>
+      <c r="D137" s="15" t="n"/>
+      <c r="E137" s="15" t="n"/>
+      <c r="F137" s="15" t="n"/>
+      <c r="G137" s="15" t="n"/>
+      <c r="H137" s="15" t="n"/>
+      <c r="I137" s="14">
         <f>IF($D137="","",$D137&amp;"|"&amp;$B137)</f>
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="I138" s="8">
+      <c r="A138" s="15" t="n"/>
+      <c r="B138" s="15" t="n"/>
+      <c r="C138" s="15" t="n"/>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
+      <c r="F138" s="15" t="n"/>
+      <c r="G138" s="15" t="n"/>
+      <c r="H138" s="15" t="n"/>
+      <c r="I138" s="14">
         <f>IF($D138="","",$D138&amp;"|"&amp;$B138)</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="I139" s="8">
+      <c r="A139" s="15" t="n"/>
+      <c r="B139" s="15" t="n"/>
+      <c r="C139" s="15" t="n"/>
+      <c r="D139" s="15" t="n"/>
+      <c r="E139" s="15" t="n"/>
+      <c r="F139" s="15" t="n"/>
+      <c r="G139" s="15" t="n"/>
+      <c r="H139" s="15" t="n"/>
+      <c r="I139" s="14">
         <f>IF($D139="","",$D139&amp;"|"&amp;$B139)</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="I140" s="8">
+      <c r="A140" s="15" t="n"/>
+      <c r="B140" s="15" t="n"/>
+      <c r="C140" s="15" t="n"/>
+      <c r="D140" s="15" t="n"/>
+      <c r="E140" s="15" t="n"/>
+      <c r="F140" s="15" t="n"/>
+      <c r="G140" s="15" t="n"/>
+      <c r="H140" s="15" t="n"/>
+      <c r="I140" s="14">
         <f>IF($D140="","",$D140&amp;"|"&amp;$B140)</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="I141" s="8">
+      <c r="A141" s="15" t="n"/>
+      <c r="B141" s="15" t="n"/>
+      <c r="C141" s="15" t="n"/>
+      <c r="D141" s="15" t="n"/>
+      <c r="E141" s="15" t="n"/>
+      <c r="F141" s="15" t="n"/>
+      <c r="G141" s="15" t="n"/>
+      <c r="H141" s="15" t="n"/>
+      <c r="I141" s="14">
         <f>IF($D141="","",$D141&amp;"|"&amp;$B141)</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="I142" s="8">
+      <c r="A142" s="15" t="n"/>
+      <c r="B142" s="15" t="n"/>
+      <c r="C142" s="15" t="n"/>
+      <c r="D142" s="15" t="n"/>
+      <c r="E142" s="15" t="n"/>
+      <c r="F142" s="15" t="n"/>
+      <c r="G142" s="15" t="n"/>
+      <c r="H142" s="15" t="n"/>
+      <c r="I142" s="14">
         <f>IF($D142="","",$D142&amp;"|"&amp;$B142)</f>
         <v/>
       </c>
     </row>
     <row r="143">
-      <c r="I143" s="8">
+      <c r="A143" s="15" t="n"/>
+      <c r="B143" s="15" t="n"/>
+      <c r="C143" s="15" t="n"/>
+      <c r="D143" s="15" t="n"/>
+      <c r="E143" s="15" t="n"/>
+      <c r="F143" s="15" t="n"/>
+      <c r="G143" s="15" t="n"/>
+      <c r="H143" s="15" t="n"/>
+      <c r="I143" s="14">
         <f>IF($D143="","",$D143&amp;"|"&amp;$B143)</f>
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="I144" s="8">
+      <c r="A144" s="15" t="n"/>
+      <c r="B144" s="15" t="n"/>
+      <c r="C144" s="15" t="n"/>
+      <c r="D144" s="15" t="n"/>
+      <c r="E144" s="15" t="n"/>
+      <c r="F144" s="15" t="n"/>
+      <c r="G144" s="15" t="n"/>
+      <c r="H144" s="15" t="n"/>
+      <c r="I144" s="14">
         <f>IF($D144="","",$D144&amp;"|"&amp;$B144)</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="I145" s="8">
+      <c r="A145" s="15" t="n"/>
+      <c r="B145" s="15" t="n"/>
+      <c r="C145" s="15" t="n"/>
+      <c r="D145" s="15" t="n"/>
+      <c r="E145" s="15" t="n"/>
+      <c r="F145" s="15" t="n"/>
+      <c r="G145" s="15" t="n"/>
+      <c r="H145" s="15" t="n"/>
+      <c r="I145" s="14">
         <f>IF($D145="","",$D145&amp;"|"&amp;$B145)</f>
         <v/>
       </c>
     </row>
     <row r="146">
-      <c r="I146" s="8">
+      <c r="A146" s="15" t="n"/>
+      <c r="B146" s="15" t="n"/>
+      <c r="C146" s="15" t="n"/>
+      <c r="D146" s="15" t="n"/>
+      <c r="E146" s="15" t="n"/>
+      <c r="F146" s="15" t="n"/>
+      <c r="G146" s="15" t="n"/>
+      <c r="H146" s="15" t="n"/>
+      <c r="I146" s="14">
         <f>IF($D146="","",$D146&amp;"|"&amp;$B146)</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="I147" s="8">
+      <c r="A147" s="15" t="n"/>
+      <c r="B147" s="15" t="n"/>
+      <c r="C147" s="15" t="n"/>
+      <c r="D147" s="15" t="n"/>
+      <c r="E147" s="15" t="n"/>
+      <c r="F147" s="15" t="n"/>
+      <c r="G147" s="15" t="n"/>
+      <c r="H147" s="15" t="n"/>
+      <c r="I147" s="14">
         <f>IF($D147="","",$D147&amp;"|"&amp;$B147)</f>
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="I148" s="8">
+      <c r="A148" s="15" t="n"/>
+      <c r="B148" s="15" t="n"/>
+      <c r="C148" s="15" t="n"/>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
+      <c r="F148" s="15" t="n"/>
+      <c r="G148" s="15" t="n"/>
+      <c r="H148" s="15" t="n"/>
+      <c r="I148" s="14">
         <f>IF($D148="","",$D148&amp;"|"&amp;$B148)</f>
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="I149" s="8">
+      <c r="A149" s="15" t="n"/>
+      <c r="B149" s="15" t="n"/>
+      <c r="C149" s="15" t="n"/>
+      <c r="D149" s="15" t="n"/>
+      <c r="E149" s="15" t="n"/>
+      <c r="F149" s="15" t="n"/>
+      <c r="G149" s="15" t="n"/>
+      <c r="H149" s="15" t="n"/>
+      <c r="I149" s="14">
         <f>IF($D149="","",$D149&amp;"|"&amp;$B149)</f>
         <v/>
       </c>
     </row>
     <row r="150">
-      <c r="I150" s="8">
+      <c r="A150" s="15" t="n"/>
+      <c r="B150" s="15" t="n"/>
+      <c r="C150" s="15" t="n"/>
+      <c r="D150" s="15" t="n"/>
+      <c r="E150" s="15" t="n"/>
+      <c r="F150" s="15" t="n"/>
+      <c r="G150" s="15" t="n"/>
+      <c r="H150" s="15" t="n"/>
+      <c r="I150" s="14">
         <f>IF($D150="","",$D150&amp;"|"&amp;$B150)</f>
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="I151" s="8">
+      <c r="A151" s="15" t="n"/>
+      <c r="B151" s="15" t="n"/>
+      <c r="C151" s="15" t="n"/>
+      <c r="D151" s="15" t="n"/>
+      <c r="E151" s="15" t="n"/>
+      <c r="F151" s="15" t="n"/>
+      <c r="G151" s="15" t="n"/>
+      <c r="H151" s="15" t="n"/>
+      <c r="I151" s="14">
         <f>IF($D151="","",$D151&amp;"|"&amp;$B151)</f>
         <v/>
       </c>
     </row>
     <row r="152">
-      <c r="I152" s="8">
+      <c r="A152" s="15" t="n"/>
+      <c r="B152" s="15" t="n"/>
+      <c r="C152" s="15" t="n"/>
+      <c r="D152" s="15" t="n"/>
+      <c r="E152" s="15" t="n"/>
+      <c r="F152" s="15" t="n"/>
+      <c r="G152" s="15" t="n"/>
+      <c r="H152" s="15" t="n"/>
+      <c r="I152" s="14">
         <f>IF($D152="","",$D152&amp;"|"&amp;$B152)</f>
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="I153" s="8">
+      <c r="A153" s="15" t="n"/>
+      <c r="B153" s="15" t="n"/>
+      <c r="C153" s="15" t="n"/>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n"/>
+      <c r="F153" s="15" t="n"/>
+      <c r="G153" s="15" t="n"/>
+      <c r="H153" s="15" t="n"/>
+      <c r="I153" s="14">
         <f>IF($D153="","",$D153&amp;"|"&amp;$B153)</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="I154" s="8">
+      <c r="A154" s="15" t="n"/>
+      <c r="B154" s="15" t="n"/>
+      <c r="C154" s="15" t="n"/>
+      <c r="D154" s="15" t="n"/>
+      <c r="E154" s="15" t="n"/>
+      <c r="F154" s="15" t="n"/>
+      <c r="G154" s="15" t="n"/>
+      <c r="H154" s="15" t="n"/>
+      <c r="I154" s="14">
         <f>IF($D154="","",$D154&amp;"|"&amp;$B154)</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="I155" s="8">
+      <c r="A155" s="15" t="n"/>
+      <c r="B155" s="15" t="n"/>
+      <c r="C155" s="15" t="n"/>
+      <c r="D155" s="15" t="n"/>
+      <c r="E155" s="15" t="n"/>
+      <c r="F155" s="15" t="n"/>
+      <c r="G155" s="15" t="n"/>
+      <c r="H155" s="15" t="n"/>
+      <c r="I155" s="14">
         <f>IF($D155="","",$D155&amp;"|"&amp;$B155)</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="I156" s="8">
+      <c r="A156" s="15" t="n"/>
+      <c r="B156" s="15" t="n"/>
+      <c r="C156" s="15" t="n"/>
+      <c r="D156" s="15" t="n"/>
+      <c r="E156" s="15" t="n"/>
+      <c r="F156" s="15" t="n"/>
+      <c r="G156" s="15" t="n"/>
+      <c r="H156" s="15" t="n"/>
+      <c r="I156" s="14">
         <f>IF($D156="","",$D156&amp;"|"&amp;$B156)</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="I157" s="8">
+      <c r="A157" s="15" t="n"/>
+      <c r="B157" s="15" t="n"/>
+      <c r="C157" s="15" t="n"/>
+      <c r="D157" s="15" t="n"/>
+      <c r="E157" s="15" t="n"/>
+      <c r="F157" s="15" t="n"/>
+      <c r="G157" s="15" t="n"/>
+      <c r="H157" s="15" t="n"/>
+      <c r="I157" s="14">
         <f>IF($D157="","",$D157&amp;"|"&amp;$B157)</f>
         <v/>
       </c>
     </row>
     <row r="158">
-      <c r="I158" s="8">
+      <c r="A158" s="15" t="n"/>
+      <c r="B158" s="15" t="n"/>
+      <c r="C158" s="15" t="n"/>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
+      <c r="F158" s="15" t="n"/>
+      <c r="G158" s="15" t="n"/>
+      <c r="H158" s="15" t="n"/>
+      <c r="I158" s="14">
         <f>IF($D158="","",$D158&amp;"|"&amp;$B158)</f>
         <v/>
       </c>
     </row>
     <row r="159">
-      <c r="I159" s="8">
+      <c r="A159" s="15" t="n"/>
+      <c r="B159" s="15" t="n"/>
+      <c r="C159" s="15" t="n"/>
+      <c r="D159" s="15" t="n"/>
+      <c r="E159" s="15" t="n"/>
+      <c r="F159" s="15" t="n"/>
+      <c r="G159" s="15" t="n"/>
+      <c r="H159" s="15" t="n"/>
+      <c r="I159" s="14">
         <f>IF($D159="","",$D159&amp;"|"&amp;$B159)</f>
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="I160" s="8">
+      <c r="A160" s="15" t="n"/>
+      <c r="B160" s="15" t="n"/>
+      <c r="C160" s="15" t="n"/>
+      <c r="D160" s="15" t="n"/>
+      <c r="E160" s="15" t="n"/>
+      <c r="F160" s="15" t="n"/>
+      <c r="G160" s="15" t="n"/>
+      <c r="H160" s="15" t="n"/>
+      <c r="I160" s="14">
         <f>IF($D160="","",$D160&amp;"|"&amp;$B160)</f>
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="I161" s="8">
+      <c r="A161" s="15" t="n"/>
+      <c r="B161" s="15" t="n"/>
+      <c r="C161" s="15" t="n"/>
+      <c r="D161" s="15" t="n"/>
+      <c r="E161" s="15" t="n"/>
+      <c r="F161" s="15" t="n"/>
+      <c r="G161" s="15" t="n"/>
+      <c r="H161" s="15" t="n"/>
+      <c r="I161" s="14">
         <f>IF($D161="","",$D161&amp;"|"&amp;$B161)</f>
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="I162" s="8">
+      <c r="A162" s="15" t="n"/>
+      <c r="B162" s="15" t="n"/>
+      <c r="C162" s="15" t="n"/>
+      <c r="D162" s="15" t="n"/>
+      <c r="E162" s="15" t="n"/>
+      <c r="F162" s="15" t="n"/>
+      <c r="G162" s="15" t="n"/>
+      <c r="H162" s="15" t="n"/>
+      <c r="I162" s="14">
         <f>IF($D162="","",$D162&amp;"|"&amp;$B162)</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="I163" s="8">
+      <c r="A163" s="15" t="n"/>
+      <c r="B163" s="15" t="n"/>
+      <c r="C163" s="15" t="n"/>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="15" t="n"/>
+      <c r="F163" s="15" t="n"/>
+      <c r="G163" s="15" t="n"/>
+      <c r="H163" s="15" t="n"/>
+      <c r="I163" s="14">
         <f>IF($D163="","",$D163&amp;"|"&amp;$B163)</f>
         <v/>
       </c>
     </row>
     <row r="164">
-      <c r="I164" s="8">
+      <c r="A164" s="15" t="n"/>
+      <c r="B164" s="15" t="n"/>
+      <c r="C164" s="15" t="n"/>
+      <c r="D164" s="15" t="n"/>
+      <c r="E164" s="15" t="n"/>
+      <c r="F164" s="15" t="n"/>
+      <c r="G164" s="15" t="n"/>
+      <c r="H164" s="15" t="n"/>
+      <c r="I164" s="14">
         <f>IF($D164="","",$D164&amp;"|"&amp;$B164)</f>
         <v/>
       </c>
     </row>
     <row r="165">
-      <c r="I165" s="8">
+      <c r="A165" s="15" t="n"/>
+      <c r="B165" s="15" t="n"/>
+      <c r="C165" s="15" t="n"/>
+      <c r="D165" s="15" t="n"/>
+      <c r="E165" s="15" t="n"/>
+      <c r="F165" s="15" t="n"/>
+      <c r="G165" s="15" t="n"/>
+      <c r="H165" s="15" t="n"/>
+      <c r="I165" s="14">
         <f>IF($D165="","",$D165&amp;"|"&amp;$B165)</f>
         <v/>
       </c>
     </row>
     <row r="166">
-      <c r="I166" s="8">
+      <c r="A166" s="15" t="n"/>
+      <c r="B166" s="15" t="n"/>
+      <c r="C166" s="15" t="n"/>
+      <c r="D166" s="15" t="n"/>
+      <c r="E166" s="15" t="n"/>
+      <c r="F166" s="15" t="n"/>
+      <c r="G166" s="15" t="n"/>
+      <c r="H166" s="15" t="n"/>
+      <c r="I166" s="14">
         <f>IF($D166="","",$D166&amp;"|"&amp;$B166)</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="I167" s="8">
+      <c r="A167" s="15" t="n"/>
+      <c r="B167" s="15" t="n"/>
+      <c r="C167" s="15" t="n"/>
+      <c r="D167" s="15" t="n"/>
+      <c r="E167" s="15" t="n"/>
+      <c r="F167" s="15" t="n"/>
+      <c r="G167" s="15" t="n"/>
+      <c r="H167" s="15" t="n"/>
+      <c r="I167" s="14">
         <f>IF($D167="","",$D167&amp;"|"&amp;$B167)</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="I168" s="8">
+      <c r="A168" s="15" t="n"/>
+      <c r="B168" s="15" t="n"/>
+      <c r="C168" s="15" t="n"/>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="15" t="n"/>
+      <c r="F168" s="15" t="n"/>
+      <c r="G168" s="15" t="n"/>
+      <c r="H168" s="15" t="n"/>
+      <c r="I168" s="14">
         <f>IF($D168="","",$D168&amp;"|"&amp;$B168)</f>
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="I169" s="8">
+      <c r="A169" s="15" t="n"/>
+      <c r="B169" s="15" t="n"/>
+      <c r="C169" s="15" t="n"/>
+      <c r="D169" s="15" t="n"/>
+      <c r="E169" s="15" t="n"/>
+      <c r="F169" s="15" t="n"/>
+      <c r="G169" s="15" t="n"/>
+      <c r="H169" s="15" t="n"/>
+      <c r="I169" s="14">
         <f>IF($D169="","",$D169&amp;"|"&amp;$B169)</f>
         <v/>
       </c>
     </row>
     <row r="170">
-      <c r="I170" s="8">
+      <c r="A170" s="15" t="n"/>
+      <c r="B170" s="15" t="n"/>
+      <c r="C170" s="15" t="n"/>
+      <c r="D170" s="15" t="n"/>
+      <c r="E170" s="15" t="n"/>
+      <c r="F170" s="15" t="n"/>
+      <c r="G170" s="15" t="n"/>
+      <c r="H170" s="15" t="n"/>
+      <c r="I170" s="14">
         <f>IF($D170="","",$D170&amp;"|"&amp;$B170)</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="I171" s="8">
+      <c r="A171" s="15" t="n"/>
+      <c r="B171" s="15" t="n"/>
+      <c r="C171" s="15" t="n"/>
+      <c r="D171" s="15" t="n"/>
+      <c r="E171" s="15" t="n"/>
+      <c r="F171" s="15" t="n"/>
+      <c r="G171" s="15" t="n"/>
+      <c r="H171" s="15" t="n"/>
+      <c r="I171" s="14">
         <f>IF($D171="","",$D171&amp;"|"&amp;$B171)</f>
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="I172" s="8">
+      <c r="A172" s="15" t="n"/>
+      <c r="B172" s="15" t="n"/>
+      <c r="C172" s="15" t="n"/>
+      <c r="D172" s="15" t="n"/>
+      <c r="E172" s="15" t="n"/>
+      <c r="F172" s="15" t="n"/>
+      <c r="G172" s="15" t="n"/>
+      <c r="H172" s="15" t="n"/>
+      <c r="I172" s="14">
         <f>IF($D172="","",$D172&amp;"|"&amp;$B172)</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="I173" s="8">
+      <c r="A173" s="15" t="n"/>
+      <c r="B173" s="15" t="n"/>
+      <c r="C173" s="15" t="n"/>
+      <c r="D173" s="15" t="n"/>
+      <c r="E173" s="15" t="n"/>
+      <c r="F173" s="15" t="n"/>
+      <c r="G173" s="15" t="n"/>
+      <c r="H173" s="15" t="n"/>
+      <c r="I173" s="14">
         <f>IF($D173="","",$D173&amp;"|"&amp;$B173)</f>
         <v/>
       </c>
     </row>
     <row r="174">
-      <c r="I174" s="8">
+      <c r="A174" s="15" t="n"/>
+      <c r="B174" s="15" t="n"/>
+      <c r="C174" s="15" t="n"/>
+      <c r="D174" s="15" t="n"/>
+      <c r="E174" s="15" t="n"/>
+      <c r="F174" s="15" t="n"/>
+      <c r="G174" s="15" t="n"/>
+      <c r="H174" s="15" t="n"/>
+      <c r="I174" s="14">
         <f>IF($D174="","",$D174&amp;"|"&amp;$B174)</f>
         <v/>
       </c>
     </row>
     <row r="175">
-      <c r="I175" s="8">
+      <c r="A175" s="15" t="n"/>
+      <c r="B175" s="15" t="n"/>
+      <c r="C175" s="15" t="n"/>
+      <c r="D175" s="15" t="n"/>
+      <c r="E175" s="15" t="n"/>
+      <c r="F175" s="15" t="n"/>
+      <c r="G175" s="15" t="n"/>
+      <c r="H175" s="15" t="n"/>
+      <c r="I175" s="14">
         <f>IF($D175="","",$D175&amp;"|"&amp;$B175)</f>
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="I176" s="8">
+      <c r="A176" s="15" t="n"/>
+      <c r="B176" s="15" t="n"/>
+      <c r="C176" s="15" t="n"/>
+      <c r="D176" s="15" t="n"/>
+      <c r="E176" s="15" t="n"/>
+      <c r="F176" s="15" t="n"/>
+      <c r="G176" s="15" t="n"/>
+      <c r="H176" s="15" t="n"/>
+      <c r="I176" s="14">
         <f>IF($D176="","",$D176&amp;"|"&amp;$B176)</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="I177" s="8">
+      <c r="A177" s="15" t="n"/>
+      <c r="B177" s="15" t="n"/>
+      <c r="C177" s="15" t="n"/>
+      <c r="D177" s="15" t="n"/>
+      <c r="E177" s="15" t="n"/>
+      <c r="F177" s="15" t="n"/>
+      <c r="G177" s="15" t="n"/>
+      <c r="H177" s="15" t="n"/>
+      <c r="I177" s="14">
         <f>IF($D177="","",$D177&amp;"|"&amp;$B177)</f>
         <v/>
       </c>
     </row>
     <row r="178">
-      <c r="I178" s="8">
+      <c r="A178" s="15" t="n"/>
+      <c r="B178" s="15" t="n"/>
+      <c r="C178" s="15" t="n"/>
+      <c r="D178" s="15" t="n"/>
+      <c r="E178" s="15" t="n"/>
+      <c r="F178" s="15" t="n"/>
+      <c r="G178" s="15" t="n"/>
+      <c r="H178" s="15" t="n"/>
+      <c r="I178" s="14">
         <f>IF($D178="","",$D178&amp;"|"&amp;$B178)</f>
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="I179" s="8">
+      <c r="A179" s="15" t="n"/>
+      <c r="B179" s="15" t="n"/>
+      <c r="C179" s="15" t="n"/>
+      <c r="D179" s="15" t="n"/>
+      <c r="E179" s="15" t="n"/>
+      <c r="F179" s="15" t="n"/>
+      <c r="G179" s="15" t="n"/>
+      <c r="H179" s="15" t="n"/>
+      <c r="I179" s="14">
         <f>IF($D179="","",$D179&amp;"|"&amp;$B179)</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="I180" s="8">
+      <c r="A180" s="15" t="n"/>
+      <c r="B180" s="15" t="n"/>
+      <c r="C180" s="15" t="n"/>
+      <c r="D180" s="15" t="n"/>
+      <c r="E180" s="15" t="n"/>
+      <c r="F180" s="15" t="n"/>
+      <c r="G180" s="15" t="n"/>
+      <c r="H180" s="15" t="n"/>
+      <c r="I180" s="14">
         <f>IF($D180="","",$D180&amp;"|"&amp;$B180)</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="I181" s="8">
+      <c r="A181" s="15" t="n"/>
+      <c r="B181" s="15" t="n"/>
+      <c r="C181" s="15" t="n"/>
+      <c r="D181" s="15" t="n"/>
+      <c r="E181" s="15" t="n"/>
+      <c r="F181" s="15" t="n"/>
+      <c r="G181" s="15" t="n"/>
+      <c r="H181" s="15" t="n"/>
+      <c r="I181" s="14">
         <f>IF($D181="","",$D181&amp;"|"&amp;$B181)</f>
         <v/>
       </c>
     </row>
     <row r="182">
-      <c r="I182" s="8">
+      <c r="A182" s="15" t="n"/>
+      <c r="B182" s="15" t="n"/>
+      <c r="C182" s="15" t="n"/>
+      <c r="D182" s="15" t="n"/>
+      <c r="E182" s="15" t="n"/>
+      <c r="F182" s="15" t="n"/>
+      <c r="G182" s="15" t="n"/>
+      <c r="H182" s="15" t="n"/>
+      <c r="I182" s="14">
         <f>IF($D182="","",$D182&amp;"|"&amp;$B182)</f>
         <v/>
       </c>
     </row>
     <row r="183">
-      <c r="I183" s="8">
+      <c r="A183" s="15" t="n"/>
+      <c r="B183" s="15" t="n"/>
+      <c r="C183" s="15" t="n"/>
+      <c r="D183" s="15" t="n"/>
+      <c r="E183" s="15" t="n"/>
+      <c r="F183" s="15" t="n"/>
+      <c r="G183" s="15" t="n"/>
+      <c r="H183" s="15" t="n"/>
+      <c r="I183" s="14">
         <f>IF($D183="","",$D183&amp;"|"&amp;$B183)</f>
         <v/>
       </c>
     </row>
     <row r="184">
-      <c r="I184" s="8">
+      <c r="A184" s="15" t="n"/>
+      <c r="B184" s="15" t="n"/>
+      <c r="C184" s="15" t="n"/>
+      <c r="D184" s="15" t="n"/>
+      <c r="E184" s="15" t="n"/>
+      <c r="F184" s="15" t="n"/>
+      <c r="G184" s="15" t="n"/>
+      <c r="H184" s="15" t="n"/>
+      <c r="I184" s="14">
         <f>IF($D184="","",$D184&amp;"|"&amp;$B184)</f>
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="I185" s="8">
+      <c r="A185" s="15" t="n"/>
+      <c r="B185" s="15" t="n"/>
+      <c r="C185" s="15" t="n"/>
+      <c r="D185" s="15" t="n"/>
+      <c r="E185" s="15" t="n"/>
+      <c r="F185" s="15" t="n"/>
+      <c r="G185" s="15" t="n"/>
+      <c r="H185" s="15" t="n"/>
+      <c r="I185" s="14">
         <f>IF($D185="","",$D185&amp;"|"&amp;$B185)</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="I186" s="8">
+      <c r="A186" s="15" t="n"/>
+      <c r="B186" s="15" t="n"/>
+      <c r="C186" s="15" t="n"/>
+      <c r="D186" s="15" t="n"/>
+      <c r="E186" s="15" t="n"/>
+      <c r="F186" s="15" t="n"/>
+      <c r="G186" s="15" t="n"/>
+      <c r="H186" s="15" t="n"/>
+      <c r="I186" s="14">
         <f>IF($D186="","",$D186&amp;"|"&amp;$B186)</f>
         <v/>
       </c>
     </row>
     <row r="187">
-      <c r="I187" s="8">
+      <c r="A187" s="15" t="n"/>
+      <c r="B187" s="15" t="n"/>
+      <c r="C187" s="15" t="n"/>
+      <c r="D187" s="15" t="n"/>
+      <c r="E187" s="15" t="n"/>
+      <c r="F187" s="15" t="n"/>
+      <c r="G187" s="15" t="n"/>
+      <c r="H187" s="15" t="n"/>
+      <c r="I187" s="14">
         <f>IF($D187="","",$D187&amp;"|"&amp;$B187)</f>
         <v/>
       </c>
     </row>
     <row r="188">
-      <c r="I188" s="8">
+      <c r="A188" s="15" t="n"/>
+      <c r="B188" s="15" t="n"/>
+      <c r="C188" s="15" t="n"/>
+      <c r="D188" s="15" t="n"/>
+      <c r="E188" s="15" t="n"/>
+      <c r="F188" s="15" t="n"/>
+      <c r="G188" s="15" t="n"/>
+      <c r="H188" s="15" t="n"/>
+      <c r="I188" s="14">
         <f>IF($D188="","",$D188&amp;"|"&amp;$B188)</f>
         <v/>
       </c>
     </row>
     <row r="189">
-      <c r="I189" s="8">
+      <c r="A189" s="15" t="n"/>
+      <c r="B189" s="15" t="n"/>
+      <c r="C189" s="15" t="n"/>
+      <c r="D189" s="15" t="n"/>
+      <c r="E189" s="15" t="n"/>
+      <c r="F189" s="15" t="n"/>
+      <c r="G189" s="15" t="n"/>
+      <c r="H189" s="15" t="n"/>
+      <c r="I189" s="14">
         <f>IF($D189="","",$D189&amp;"|"&amp;$B189)</f>
         <v/>
       </c>
     </row>
     <row r="190">
-      <c r="I190" s="8">
+      <c r="A190" s="15" t="n"/>
+      <c r="B190" s="15" t="n"/>
+      <c r="C190" s="15" t="n"/>
+      <c r="D190" s="15" t="n"/>
+      <c r="E190" s="15" t="n"/>
+      <c r="F190" s="15" t="n"/>
+      <c r="G190" s="15" t="n"/>
+      <c r="H190" s="15" t="n"/>
+      <c r="I190" s="14">
         <f>IF($D190="","",$D190&amp;"|"&amp;$B190)</f>
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="I191" s="8">
+      <c r="A191" s="15" t="n"/>
+      <c r="B191" s="15" t="n"/>
+      <c r="C191" s="15" t="n"/>
+      <c r="D191" s="15" t="n"/>
+      <c r="E191" s="15" t="n"/>
+      <c r="F191" s="15" t="n"/>
+      <c r="G191" s="15" t="n"/>
+      <c r="H191" s="15" t="n"/>
+      <c r="I191" s="14">
         <f>IF($D191="","",$D191&amp;"|"&amp;$B191)</f>
         <v/>
       </c>
     </row>
     <row r="192">
-      <c r="I192" s="8">
+      <c r="A192" s="15" t="n"/>
+      <c r="B192" s="15" t="n"/>
+      <c r="C192" s="15" t="n"/>
+      <c r="D192" s="15" t="n"/>
+      <c r="E192" s="15" t="n"/>
+      <c r="F192" s="15" t="n"/>
+      <c r="G192" s="15" t="n"/>
+      <c r="H192" s="15" t="n"/>
+      <c r="I192" s="14">
         <f>IF($D192="","",$D192&amp;"|"&amp;$B192)</f>
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="I193" s="8">
+      <c r="A193" s="15" t="n"/>
+      <c r="B193" s="15" t="n"/>
+      <c r="C193" s="15" t="n"/>
+      <c r="D193" s="15" t="n"/>
+      <c r="E193" s="15" t="n"/>
+      <c r="F193" s="15" t="n"/>
+      <c r="G193" s="15" t="n"/>
+      <c r="H193" s="15" t="n"/>
+      <c r="I193" s="14">
         <f>IF($D193="","",$D193&amp;"|"&amp;$B193)</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="I194" s="8">
+      <c r="A194" s="15" t="n"/>
+      <c r="B194" s="15" t="n"/>
+      <c r="C194" s="15" t="n"/>
+      <c r="D194" s="15" t="n"/>
+      <c r="E194" s="15" t="n"/>
+      <c r="F194" s="15" t="n"/>
+      <c r="G194" s="15" t="n"/>
+      <c r="H194" s="15" t="n"/>
+      <c r="I194" s="14">
         <f>IF($D194="","",$D194&amp;"|"&amp;$B194)</f>
         <v/>
       </c>
     </row>
     <row r="195">
-      <c r="I195" s="8">
+      <c r="A195" s="15" t="n"/>
+      <c r="B195" s="15" t="n"/>
+      <c r="C195" s="15" t="n"/>
+      <c r="D195" s="15" t="n"/>
+      <c r="E195" s="15" t="n"/>
+      <c r="F195" s="15" t="n"/>
+      <c r="G195" s="15" t="n"/>
+      <c r="H195" s="15" t="n"/>
+      <c r="I195" s="14">
         <f>IF($D195="","",$D195&amp;"|"&amp;$B195)</f>
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="I196" s="8">
+      <c r="A196" s="15" t="n"/>
+      <c r="B196" s="15" t="n"/>
+      <c r="C196" s="15" t="n"/>
+      <c r="D196" s="15" t="n"/>
+      <c r="E196" s="15" t="n"/>
+      <c r="F196" s="15" t="n"/>
+      <c r="G196" s="15" t="n"/>
+      <c r="H196" s="15" t="n"/>
+      <c r="I196" s="14">
         <f>IF($D196="","",$D196&amp;"|"&amp;$B196)</f>
         <v/>
       </c>
     </row>
     <row r="197">
-      <c r="I197" s="8">
+      <c r="A197" s="15" t="n"/>
+      <c r="B197" s="15" t="n"/>
+      <c r="C197" s="15" t="n"/>
+      <c r="D197" s="15" t="n"/>
+      <c r="E197" s="15" t="n"/>
+      <c r="F197" s="15" t="n"/>
+      <c r="G197" s="15" t="n"/>
+      <c r="H197" s="15" t="n"/>
+      <c r="I197" s="14">
         <f>IF($D197="","",$D197&amp;"|"&amp;$B197)</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="I198" s="8">
+      <c r="A198" s="15" t="n"/>
+      <c r="B198" s="15" t="n"/>
+      <c r="C198" s="15" t="n"/>
+      <c r="D198" s="15" t="n"/>
+      <c r="E198" s="15" t="n"/>
+      <c r="F198" s="15" t="n"/>
+      <c r="G198" s="15" t="n"/>
+      <c r="H198" s="15" t="n"/>
+      <c r="I198" s="14">
         <f>IF($D198="","",$D198&amp;"|"&amp;$B198)</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="I199" s="8">
+      <c r="A199" s="15" t="n"/>
+      <c r="B199" s="15" t="n"/>
+      <c r="C199" s="15" t="n"/>
+      <c r="D199" s="15" t="n"/>
+      <c r="E199" s="15" t="n"/>
+      <c r="F199" s="15" t="n"/>
+      <c r="G199" s="15" t="n"/>
+      <c r="H199" s="15" t="n"/>
+      <c r="I199" s="14">
         <f>IF($D199="","",$D199&amp;"|"&amp;$B199)</f>
         <v/>
       </c>
     </row>
     <row r="200">
-      <c r="I200" s="8">
+      <c r="A200" s="15" t="n"/>
+      <c r="B200" s="15" t="n"/>
+      <c r="C200" s="15" t="n"/>
+      <c r="D200" s="15" t="n"/>
+      <c r="E200" s="15" t="n"/>
+      <c r="F200" s="15" t="n"/>
+      <c r="G200" s="15" t="n"/>
+      <c r="H200" s="15" t="n"/>
+      <c r="I200" s="14">
         <f>IF($D200="","",$D200&amp;"|"&amp;$B200)</f>
         <v/>
       </c>
